--- a/Cards.xlsx
+++ b/Cards.xlsx
@@ -5,13 +5,61 @@
     <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId4"/>
+    <sheet name="Export Summary" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet 1" sheetId="2" r:id="rId6"/>
+    <sheet name="Sheet 2 - Базовые переменные" sheetId="3" r:id="rId7"/>
+    <sheet name="Sheet 2 - Синие карты" sheetId="4" r:id="rId8"/>
+    <sheet name="Sheet 2 - Красные карты" sheetId="5" r:id="rId9"/>
+    <sheet name="Sheet 2 - Вероятность выпадения" sheetId="6" r:id="rId10"/>
+    <sheet name="Sheet 2 - Баланс игроков в ход " sheetId="7" r:id="rId11"/>
+    <sheet name="Sheet 2 - Фиолетовые карты" sheetId="8" r:id="rId12"/>
+    <sheet name="Sheet 2 - Золотые карты" sheetId="9" r:id="rId13"/>
   </sheets>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="180">
+  <si>
+    <t>This document was exported from Numbers.  Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
+  </si>
+  <si>
+    <t>Numbers Sheet Name</t>
+  </si>
+  <si>
+    <t>Numbers Table Name</t>
+  </si>
+  <si>
+    <t>Excel Worksheet Name</t>
+  </si>
+  <si>
+    <t>Sheet 1</t>
+  </si>
+  <si>
+    <t>Table 1</t>
+  </si>
   <si>
     <t>Name</t>
   </si>
@@ -40,308 +88,542 @@
     <t>Narrative</t>
   </si>
   <si>
-    <t>Пенсия пришла!</t>
+    <t>Кофе-брейк от Искандера</t>
   </si>
   <si>
     <t>Blue</t>
   </si>
   <si>
+    <t>GETALL 1</t>
+  </si>
+  <si>
+    <t>cartoon professor Iskander holding coffee cup, warm blue lighting, game dev classroom background, playful academic vibe, soft shadows, vibrant colors</t>
+  </si>
+  <si>
+    <t>Когда лекция по экономике затянулась, Искандер угощает всех.</t>
+  </si>
+  <si>
+    <t>+1 корм всем</t>
+  </si>
+  <si>
+    <t>Методичка в общий чат</t>
+  </si>
+  <si>
     <t>GETALL 2</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>pensia.jpg</t>
-  </si>
-  <si>
-    <t>Бабушки довольны</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>+2 монеты всем</t>
-  </si>
-  <si>
-    <t>Налоговые каникулы</t>
+    <t>friendly Konstantin sharing colorful documentation on tablet, blue glow, modern university setting, semi-realistic cartoon style, UI elements floating</t>
+  </si>
+  <si>
+    <t>Константин выложил гайд в чат — команда сыта и мотивирована.</t>
+  </si>
+  <si>
+    <t>Баланс-пати от Константина</t>
   </si>
   <si>
     <t>GETALL 3</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>new_year.png</t>
-  </si>
-  <si>
-    <t>С Новай годай!</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>+3 монеты всем</t>
-  </si>
-  <si>
-    <t>Фестиваль еды</t>
-  </si>
-  <si>
-    <t>GETALL 1</t>
-  </si>
-  <si>
-    <t>food.jpg</t>
-  </si>
-  <si>
-    <t>Шаурма за счёт мэра</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>+1 монета всем</t>
-  </si>
-  <si>
-    <t>Премия от спонсора</t>
+    <t>team celebration with game balance charts, blue confetti, cartoon style, professors in background, food icons floating</t>
+  </si>
+  <si>
+    <t>После успешной балансировки — мини-праздник.</t>
+  </si>
+  <si>
+    <t>+2 корма всем</t>
+  </si>
+  <si>
+    <t>Синхронизация спринта</t>
   </si>
   <si>
     <t>GETALL 4</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>primia.jpg</t>
-  </si>
-  <si>
-    <t>Щедрый олигарх</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>+4 монеты всем</t>
-  </si>
-  <si>
-    <t>Стипендия</t>
+    <t>agile board with sticky notes, blue hour lighting, cartoon developers high-fiving, food power-ups appearing</t>
+  </si>
+  <si>
+    <t>Спринт синхронизирован, команда в ресурсе.</t>
+  </si>
+  <si>
+    <t>Грант на корм для команды</t>
   </si>
   <si>
     <t>GETALL 5</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>stipendia.jpg</t>
-  </si>
-  <si>
-    <t>Ура стипа!</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>+5 монет всем</t>
-  </si>
-  <si>
-    <t>Агрессивный коллектор</t>
+    <t>golden grant certificate with food icons, blue sparkles, cartoon Iskander presenting, game dev lab background</t>
+  </si>
+  <si>
+    <t>Внешнее финансирование найдено!</t>
+  </si>
+  <si>
+    <t>+3 корма всем</t>
+  </si>
+  <si>
+    <t>Лекция про экономику корма</t>
+  </si>
+  <si>
+    <t>GETALL 6</t>
+  </si>
+  <si>
+    <t>Iskander at whiteboard with economic graphs made of food, blue spotlight, playful cartoon, students taking notes</t>
+  </si>
+  <si>
+    <t>Искандер объясняет, как корм влияет на метрики.</t>
+  </si>
+  <si>
+    <t>Дедлайн продлён!</t>
+  </si>
+  <si>
+    <t>GETALL 7</t>
+  </si>
+  <si>
+    <t>relieved students celebrating, calendar with extended date, blue confetti, cartoon style, food appearing magically</t>
+  </si>
+  <si>
+    <t>Невероятно! Дедлайн сдвинули. Время на подкрепление.</t>
+  </si>
+  <si>
+    <t>+4 корма всем</t>
+  </si>
+  <si>
+    <t>Командный бонус от Искандера</t>
+  </si>
+  <si>
+    <t>GETALL 8</t>
+  </si>
+  <si>
+    <t>Iskander distributing golden food tokens, blue aura, cartoon academic setting, happy student avatars</t>
+  </si>
+  <si>
+    <t>За успешный этап — бонус от преподавателя.</t>
+  </si>
+  <si>
+    <t>Защита проекта — всем плюс</t>
+  </si>
+  <si>
+    <t>GETALL 9</t>
+  </si>
+  <si>
+    <t>presentation stage with applause, blue spotlight, cartoon professors clapping, food rewards floating</t>
+  </si>
+  <si>
+    <t>Проект защищён на отлично! Преподаватели щедры.</t>
+  </si>
+  <si>
+    <t>+5 кормов всем</t>
+  </si>
+  <si>
+    <t>Финальный релиз: корм для всех</t>
+  </si>
+  <si>
+    <t>GETALL 10</t>
+  </si>
+  <si>
+    <t>game launch celebration, blue fireworks, cartoon team with controllers, golden food raining down</t>
+  </si>
+  <si>
+    <t>Релиз состоялся! Все получают награду.</t>
+  </si>
+  <si>
+    <t>Аудит кормов от Искандера</t>
   </si>
   <si>
     <t>Red</t>
   </si>
   <si>
+    <t>STEAL_MONEY ALL 1</t>
+  </si>
+  <si>
+    <t>cartoon Iskander with magnifying glass inspecting ledger, dramatic red lighting, playful stern expression, game economy charts</t>
+  </si>
+  <si>
+    <t>Искандер проверяет бюджет. Найдены излишки — изымаются.</t>
+  </si>
+  <si>
+    <t>Заберите 1 корм у всех оппонентов</t>
+  </si>
+  <si>
+    <t>Проверка ТЗ: штраф за ошибки</t>
+  </si>
+  <si>
+    <t>STEAL_MONEY ALL 2</t>
+  </si>
+  <si>
+    <t>Konstantin with red pen marking documents, shadows, humorous intense expression, game dev office background, floating error icons</t>
+  </si>
+  <si>
+    <t>Константин нашёл несоответствия в ТЗ. Штрафуем.</t>
+  </si>
+  <si>
+    <t>Заберите 2 корма у всех оппонентов</t>
+  </si>
+  <si>
+    <t>Ревизия спринта</t>
+  </si>
+  <si>
     <t>STEAL_MONEY ALL 3</t>
   </si>
   <si>
-    <t>collector.jpg</t>
-  </si>
-  <si>
-    <t>Деньги есть?</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>Крадет 3 монеты у всех</t>
-  </si>
-  <si>
-    <t>Проверка пожарной</t>
-  </si>
-  <si>
-    <t>STEAL_MONEY ALL 2</t>
-  </si>
-  <si>
-    <t>pojarniy.jpg</t>
-  </si>
-  <si>
-    <t>Есть огнетушитель?</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>Крадет 2 монеты у всех</t>
-  </si>
-  <si>
-    <t>Рэкетир на районе</t>
-  </si>
-  <si>
-    <t>STEAL_MONEY RANDOM 5</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>thief.jpg</t>
-  </si>
-  <si>
-    <t>Вор в законе</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>Крадет 5 монет у случайного</t>
-  </si>
-  <si>
-    <t>Коррупционный скандал</t>
+    <t>agile board under red spotlight, cartoon auditor figure, sticky notes flying, food tokens being collected</t>
+  </si>
+  <si>
+    <t>Внезапная ревизия! Ресурсы перераспределяются.</t>
+  </si>
+  <si>
+    <t>Заберите 3 корма у всех оппонентов</t>
+  </si>
+  <si>
+    <t>Константин требует отчёт</t>
   </si>
   <si>
     <t>STEAL_MONEY ALL 4</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>no_money.png</t>
-  </si>
-  <si>
-    <t>Чиновники нашли способ пополнить казну.</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>Крадет 4 монеты у всех</t>
-  </si>
-  <si>
-    <t>Внезапный акциз</t>
+    <t>Konstantin holding clipboard with checklist, red glow, semi-serious cartoon, students scrambling, food icons moving</t>
+  </si>
+  <si>
+    <t>«Где отчёт?» — спрашивает Константин. Придётся поделиться.</t>
+  </si>
+  <si>
+    <t>Заберите 4 корма у всех оппонентов</t>
+  </si>
+  <si>
+    <t>Нерф баланса: забираем корм</t>
+  </si>
+  <si>
+    <t>STEAL_MONEY ALL 5</t>
+  </si>
+  <si>
+    <t>game balance scale tipping, red particle effects, cartoon Iskander adjusting sliders, food being redistributed</t>
+  </si>
+  <si>
+    <t>Баланс нарушен? Исправляем!</t>
+  </si>
+  <si>
+    <t>Заберите 5 кормов у всех оппонентов</t>
+  </si>
+  <si>
+    <t>Дедлайн вчера: конфискация</t>
   </si>
   <si>
     <t>STEAL_MONEY ALL 6</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>stonks.jpg</t>
-  </si>
-  <si>
-    <t>Утильсбор</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>Крадет 6 монет у всех</t>
-  </si>
-  <si>
-    <t>Золотая жила</t>
+    <t>calendar with yesterday's date highlighted red, cartoon professor pointing, food tokens flying away, humorous panic</t>
+  </si>
+  <si>
+    <t>Дедлайн был вчера. Конфискация ресурсов.</t>
+  </si>
+  <si>
+    <t>Заберите 6 кормов у всех оппонентов</t>
+  </si>
+  <si>
+    <t>Патч 1.0: изъятие ресурсов</t>
+  </si>
+  <si>
+    <t>STEAL_MONEY ALL 7</t>
+  </si>
+  <si>
+    <t>software patch notes with red highlights, cartoon developer applying fix, food icons being collected, game UI style</t>
+  </si>
+  <si>
+    <t>Вышел патч с баланс-изменениями.</t>
+  </si>
+  <si>
+    <t>Заберите 7 кормов у всех оппонентов</t>
+  </si>
+  <si>
+    <t>Искандер пересчитал баланс</t>
+  </si>
+  <si>
+    <t>STEAL_MONEY ALL 8</t>
+  </si>
+  <si>
+    <t>Iskander with calculator and economic graphs, red spotlight, cartoon style, food tokens flowing to one player</t>
+  </si>
+  <si>
+    <t>После перерасчёта экономика требует жертв.</t>
+  </si>
+  <si>
+    <t>Заберите 8 кормов у всех оппонентов</t>
+  </si>
+  <si>
+    <t>Константин нашёл баги в вашей документации</t>
+  </si>
+  <si>
+    <t>STEAL_MONEY ALL 9</t>
+  </si>
+  <si>
+    <t>Konstantin with bug report, red stamps, cartoon frustrated students, food icons being confiscated, humorous office scene</t>
+  </si>
+  <si>
+    <t>«Это не баг, это фича?» — не прокатит.</t>
+  </si>
+  <si>
+    <t>Заберите 9 кормов у всех оппонентов</t>
+  </si>
+  <si>
+    <t>Финальная аттестация: корм на кону</t>
+  </si>
+  <si>
+    <t>STEAL_MONEY ALL 10</t>
+  </si>
+  <si>
+    <t>exam hall with red lighting, cartoon professors at table, food tokens as stakes, dramatic but playful style</t>
+  </si>
+  <si>
+    <t>Аттестация решает всё. Победитель забирает ресурсы.</t>
+  </si>
+  <si>
+    <t>Заберите 10 кормов у всех оппонентов</t>
+  </si>
+  <si>
+    <t>Плагиат на митапе</t>
+  </si>
+  <si>
+    <t>Purple</t>
+  </si>
+  <si>
+    <t>STEAL_CARD RANDOM</t>
+  </si>
+  <si>
+    <t>Карта</t>
+  </si>
+  <si>
+    <t>mysterious silhouette sneaking a card from table, purple neon glow, game jam night atmosphere, stylized cartoon, subtle humor</t>
+  </si>
+  <si>
+    <t>Пока все обсуждали архитектуру, вы тихонько взяли чужую идею...</t>
+  </si>
+  <si>
+    <t>Украдите случайную карту у случайного соперника</t>
+  </si>
+  <si>
+    <t>Стипендия за проект</t>
   </si>
   <si>
     <t>Gold</t>
   </si>
   <si>
-    <t>GET 10</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>gold.jpg</t>
-  </si>
-  <si>
-    <t>Нашли нефть под гаражом</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>+10 монет</t>
-  </si>
-  <si>
-    <t>Инвестор из Дубая</t>
-  </si>
-  <si>
-    <t>GET 8</t>
-  </si>
-  <si>
-    <t>sahnov.png</t>
-  </si>
-  <si>
-    <t>Вы были приглашены в студию</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>+8 монет</t>
-  </si>
-  <si>
-    <t>Лотерейный билет</t>
-  </si>
-  <si>
-    <t>GET 15</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>casino.jpg</t>
-  </si>
-  <si>
-    <t>Джекпот!</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>+15 монет</t>
-  </si>
-  <si>
-    <t>Рейдерский захват</t>
-  </si>
-  <si>
-    <t>Purple</t>
-  </si>
-  <si>
-    <t>STEAL_CARD RANDOM</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>raider.jpg</t>
-  </si>
-  <si>
-    <t>На нас напали!</t>
-  </si>
-  <si>
-    <t>Крадет карту у случайного</t>
+    <t>GET 1</t>
+  </si>
+  <si>
+    <t>golden coin with game controller icon, radiant light, cartoon scholarship envelope, celebratory particles, warm tones</t>
+  </si>
+  <si>
+    <t>Ваш проект заметили! Первая выплата.</t>
+  </si>
+  <si>
+    <t>Получите 1 корм из банка</t>
+  </si>
+  <si>
+    <t>Грант на балансировку</t>
+  </si>
+  <si>
+    <t>GET 2</t>
+  </si>
+  <si>
+    <t>grant document with golden seal, Iskander signing, cartoon style, food tokens appearing, soft golden glow</t>
+  </si>
+  <si>
+    <t>Специальный грант на улучшение баланса.</t>
+  </si>
+  <si>
+    <t>Получите 2 корма из банка</t>
+  </si>
+  <si>
+    <t>Инвестиции от Искандера</t>
+  </si>
+  <si>
+    <t>GET 3</t>
+  </si>
+  <si>
+    <t>Iskander as angel investor with golden briefcase, sparkles, cartoon academic setting, food rewards materializing</t>
+  </si>
+  <si>
+    <t>Искандер верит в ваш проект! Крупные инвестиции.</t>
+  </si>
+  <si>
+    <t>Получите 3 корма из банка</t>
+  </si>
+  <si>
+    <t>Sheet 2</t>
+  </si>
+  <si>
+    <t>Базовые переменные</t>
+  </si>
+  <si>
+    <t>Sheet 2 - Базовые переменные</t>
+  </si>
+  <si>
+    <t>Переменная</t>
+  </si>
+  <si>
+    <t>Значение</t>
+  </si>
+  <si>
+    <t>Стартовый баланс, мин.</t>
+  </si>
+  <si>
+    <t>Стартовый баланс, макс.</t>
+  </si>
+  <si>
+    <t>Цель победы</t>
+  </si>
+  <si>
+    <t>Золото за ход</t>
+  </si>
+  <si>
+    <t>Кол-во игроков</t>
+  </si>
+  <si>
+    <t>Минимальное кол-во раундов</t>
+  </si>
+  <si>
+    <t>Максимальное кол-во раундов</t>
+  </si>
+  <si>
+    <t>Синие карты</t>
+  </si>
+  <si>
+    <t>Sheet 2 - Синие карты</t>
+  </si>
+  <si>
+    <t>№</t>
+  </si>
+  <si>
+    <t>Цвет</t>
+  </si>
+  <si>
+    <t>Стоимость</t>
+  </si>
+  <si>
+    <t>Доход за ход</t>
+  </si>
+  <si>
+    <t>Средняя прибыль за игру</t>
+  </si>
+  <si>
+    <t>Синий</t>
+  </si>
+  <si>
+    <t>СРЕДНЯЯ ценность за ход</t>
+  </si>
+  <si>
+    <t>Красные карты</t>
+  </si>
+  <si>
+    <t>Sheet 2 - Красные карты</t>
+  </si>
+  <si>
+    <t>Красный</t>
+  </si>
+  <si>
+    <t>Вероятность выпадения цвета</t>
+  </si>
+  <si>
+    <t>Sheet 2 - Вероятность выпадения</t>
+  </si>
+  <si>
+    <t>Вероятность</t>
+  </si>
+  <si>
+    <t>Фиолетовый</t>
+  </si>
+  <si>
+    <t>Золотой</t>
+  </si>
+  <si>
+    <t>Баланс игроков в ход (суммарно)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sheet 2 - Баланс игроков в ход </t>
+  </si>
+  <si>
+    <t>Средний доход с карт</t>
+  </si>
+  <si>
+    <t>Ход</t>
+  </si>
+  <si>
+    <t>Заработано всегда</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="1"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t>Синий</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="1"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t>Красный</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="1"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t>Фиолетовый</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="1"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t>Золотой</t>
+    </r>
+  </si>
+  <si>
+    <t>Средне заработано</t>
+  </si>
+  <si>
+    <t>Средне потрачено на игрока</t>
+  </si>
+  <si>
+    <t>Средне на игрока</t>
+  </si>
+  <si>
+    <t>Фиолетовые карты</t>
+  </si>
+  <si>
+    <t>Sheet 2 - Фиолетовые карты</t>
+  </si>
+  <si>
+    <t>Золотые карты</t>
+  </si>
+  <si>
+    <t>Sheet 2 - Золотые карты</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="0" formatCode="General"/>
+    <numFmt numFmtId="59" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -353,13 +635,29 @@
       <name val="Helvetica Neue"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color indexed="8"/>
+      <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="12"/>
+      <color indexed="11"/>
+      <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Helvetica Neue"/>
+    </font>
+    <font>
       <b val="1"/>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -374,7 +672,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="12"/>
+        <fgColor indexed="10"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="14"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="15"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="16"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="17"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="18"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="19"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
@@ -389,106 +723,106 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
+        <color indexed="12"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="12"/>
       </right>
       <top style="thin">
-        <color indexed="10"/>
+        <color indexed="12"/>
       </top>
       <bottom style="thin">
-        <color indexed="11"/>
+        <color indexed="13"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
+        <color indexed="12"/>
       </left>
       <right style="thin">
-        <color indexed="11"/>
+        <color indexed="13"/>
       </right>
       <top style="thin">
-        <color indexed="11"/>
+        <color indexed="13"/>
       </top>
       <bottom style="thin">
-        <color indexed="10"/>
+        <color indexed="12"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="11"/>
+        <color indexed="13"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="12"/>
       </right>
       <top style="thin">
-        <color indexed="11"/>
+        <color indexed="13"/>
       </top>
       <bottom style="thin">
-        <color indexed="10"/>
+        <color indexed="12"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
+        <color indexed="12"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="12"/>
       </right>
       <top style="thin">
-        <color indexed="11"/>
+        <color indexed="13"/>
       </top>
       <bottom style="thin">
-        <color indexed="10"/>
+        <color indexed="12"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
+        <color indexed="12"/>
       </left>
       <right style="thin">
-        <color indexed="11"/>
+        <color indexed="13"/>
       </right>
       <top style="thin">
-        <color indexed="10"/>
+        <color indexed="12"/>
       </top>
       <bottom style="thin">
-        <color indexed="10"/>
+        <color indexed="12"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="11"/>
+        <color indexed="13"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="12"/>
       </right>
       <top style="thin">
-        <color indexed="10"/>
+        <color indexed="12"/>
       </top>
       <bottom style="thin">
-        <color indexed="10"/>
+        <color indexed="12"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
+        <color indexed="12"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="12"/>
       </right>
       <top style="thin">
-        <color indexed="10"/>
+        <color indexed="12"/>
       </top>
       <bottom style="thin">
-        <color indexed="10"/>
+        <color indexed="12"/>
       </bottom>
       <diagonal/>
     </border>
@@ -498,32 +832,221 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="7" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="7" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="7" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="9" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="9" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="1" fontId="0" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="1" fontId="0" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="9" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="0" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="8" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="8" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -543,9 +1066,16 @@
       <rgbColor rgb="ffff00ff"/>
       <rgbColor rgb="ff00ffff"/>
       <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffbdc0bf"/>
+      <rgbColor rgb="ff5e88b1"/>
+      <rgbColor rgb="ffeef3f4"/>
+      <rgbColor rgb="ff0000ff"/>
       <rgbColor rgb="ffa5a5a5"/>
       <rgbColor rgb="ff3f3f3f"/>
+      <rgbColor rgb="ff56c1fe"/>
+      <rgbColor rgb="ffff968c"/>
+      <rgbColor rgb="ffff94ca"/>
+      <rgbColor rgb="fffff056"/>
+      <rgbColor rgb="ffbdc0bf"/>
       <rgbColor rgb="ffdbdbdb"/>
     </indexedColors>
   </colors>
@@ -1575,446 +2105,865 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I15"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="13" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="2" customWidth="1"/>
+    <col min="2" max="4" width="33.6016" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" ht="50" customHeight="1">
+      <c r="B3" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+    </row>
+    <row r="7">
+      <c r="B7" t="s" s="2">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="s" s="3">
+        <v>4</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="4"/>
+      <c r="C10" t="s" s="4">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="s" s="3">
+        <v>135</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="4"/>
+      <c r="C12" t="s" s="4">
+        <v>136</v>
+      </c>
+      <c r="D12" t="s" s="5">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="4"/>
+      <c r="C13" t="s" s="4">
+        <v>147</v>
+      </c>
+      <c r="D13" t="s" s="5">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="4"/>
+      <c r="C14" t="s" s="4">
+        <v>156</v>
+      </c>
+      <c r="D14" t="s" s="5">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="4"/>
+      <c r="C15" t="s" s="4">
+        <v>159</v>
+      </c>
+      <c r="D15" t="s" s="5">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4"/>
+      <c r="C16" t="s" s="4">
+        <v>164</v>
+      </c>
+      <c r="D16" t="s" s="5">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="4"/>
+      <c r="C17" t="s" s="4">
+        <v>176</v>
+      </c>
+      <c r="D17" t="s" s="5">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="4"/>
+      <c r="C18" t="s" s="4">
+        <v>178</v>
+      </c>
+      <c r="D18" t="s" s="5">
+        <v>179</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="D10" location="'Sheet 1'!R1C1" tooltip="" display="Sheet 1"/>
+    <hyperlink ref="D12" location="'Sheet 2 - Базовые переменные'!R2C1" tooltip="" display="Sheet 2 - Базовые переменные"/>
+    <hyperlink ref="D13" location="'Sheet 2 - Синие карты'!R2C1" tooltip="" display="Sheet 2 - Синие карты"/>
+    <hyperlink ref="D14" location="'Sheet 2 - Красные карты'!R2C1" tooltip="" display="Sheet 2 - Красные карты"/>
+    <hyperlink ref="D15" location="'Sheet 2 - Вероятность выпадения'!R2C1" tooltip="" display="Sheet 2 - Вероятность выпадения"/>
+    <hyperlink ref="D16" location="'Sheet 2 - Баланс игроков в ход '!R2C1" tooltip="" display="Sheet 2 - Баланс игроков в ход "/>
+    <hyperlink ref="D17" location="'Sheet 2 - Фиолетовые карты'!R2C1" tooltip="" display="Sheet 2 - Фиолетовые карты"/>
+    <hyperlink ref="D18" location="'Sheet 2 - Золотые карты'!R2C1" tooltip="" display="Sheet 2 - Золотые карты"/>
+  </hyperlinks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="9" width="16.3516" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="16.3516" style="1" customWidth="1"/>
+    <col min="1" max="9" width="16.3516" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="16.3516" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customHeight="1">
-      <c r="A1" t="s" s="2">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s" s="2">
+    <row r="1" ht="20.2" customHeight="1">
+      <c r="A1" t="s" s="7">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s" s="7">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s" s="7">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s" s="7">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s" s="7">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s" s="7">
+        <v>11</v>
+      </c>
+      <c r="G1" t="s" s="7">
+        <v>12</v>
+      </c>
+      <c r="H1" t="s" s="7">
+        <v>13</v>
+      </c>
+      <c r="I1" t="s" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" ht="184.2" customHeight="1">
+      <c r="A2" t="s" s="8">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="9">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s" s="10">
+        <v>17</v>
+      </c>
+      <c r="D2" s="11">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="2">
+      <c r="E2" s="11">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s" s="10">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s" s="10">
+        <v>19</v>
+      </c>
+      <c r="H2" s="11">
+        <v>10</v>
+      </c>
+      <c r="I2" t="s" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" ht="184" customHeight="1">
+      <c r="A3" t="s" s="12">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s" s="13">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s" s="14">
+        <v>22</v>
+      </c>
+      <c r="D3" s="15">
+        <v>1</v>
+      </c>
+      <c r="E3" s="15">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="2">
+      <c r="F3" t="s" s="14">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s" s="14">
+        <v>24</v>
+      </c>
+      <c r="H3" s="15">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s" s="14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" ht="148" customHeight="1">
+      <c r="A4" t="s" s="12">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s" s="13">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s" s="14">
+        <v>26</v>
+      </c>
+      <c r="D4" s="15">
+        <v>2</v>
+      </c>
+      <c r="E4" s="15">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="2">
+      <c r="F4" t="s" s="14">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s" s="14">
+        <v>28</v>
+      </c>
+      <c r="H4" s="15">
+        <v>10</v>
+      </c>
+      <c r="I4" t="s" s="14">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" ht="124" customHeight="1">
+      <c r="A5" t="s" s="12">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s" s="13">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s" s="14">
+        <v>31</v>
+      </c>
+      <c r="D5" s="15">
+        <v>2</v>
+      </c>
+      <c r="E5" s="15">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="2">
+      <c r="F5" t="s" s="14">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s" s="14">
+        <v>33</v>
+      </c>
+      <c r="H5" s="15">
+        <v>10</v>
+      </c>
+      <c r="I5" t="s" s="14">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" ht="124" customHeight="1">
+      <c r="A6" t="s" s="12">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s" s="13">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s" s="14">
+        <v>35</v>
+      </c>
+      <c r="D6" s="15">
+        <v>3</v>
+      </c>
+      <c r="E6" s="15">
         <v>5</v>
       </c>
-      <c r="G1" t="s" s="2">
+      <c r="F6" t="s" s="14">
+        <v>36</v>
+      </c>
+      <c r="G6" t="s" s="14">
+        <v>37</v>
+      </c>
+      <c r="H6" s="15">
+        <v>10</v>
+      </c>
+      <c r="I6" t="s" s="14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" ht="136" customHeight="1">
+      <c r="A7" t="s" s="12">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s" s="13">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s" s="14">
+        <v>40</v>
+      </c>
+      <c r="D7" s="15">
+        <v>3</v>
+      </c>
+      <c r="E7" s="15">
         <v>6</v>
       </c>
-      <c r="H1" t="s" s="2">
+      <c r="F7" t="s" s="14">
+        <v>41</v>
+      </c>
+      <c r="G7" t="s" s="14">
+        <v>42</v>
+      </c>
+      <c r="H7" s="15">
+        <v>10</v>
+      </c>
+      <c r="I7" t="s" s="14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" ht="148" customHeight="1">
+      <c r="A8" t="s" s="12">
+        <v>43</v>
+      </c>
+      <c r="B8" t="s" s="13">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s" s="14">
+        <v>44</v>
+      </c>
+      <c r="D8" s="15">
+        <v>4</v>
+      </c>
+      <c r="E8" s="15">
         <v>7</v>
       </c>
-      <c r="I1" t="s" s="2">
+      <c r="F8" t="s" s="14">
+        <v>45</v>
+      </c>
+      <c r="G8" t="s" s="14">
+        <v>46</v>
+      </c>
+      <c r="H8" s="15">
+        <v>10</v>
+      </c>
+      <c r="I8" t="s" s="14">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" ht="124" customHeight="1">
+      <c r="A9" t="s" s="12">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s" s="13">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s" s="14">
+        <v>49</v>
+      </c>
+      <c r="D9" s="15">
+        <v>4</v>
+      </c>
+      <c r="E9" s="15">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" ht="32.25" customHeight="1">
-      <c r="A2" t="s" s="3">
+      <c r="F9" t="s" s="14">
+        <v>50</v>
+      </c>
+      <c r="G9" t="s" s="14">
+        <v>51</v>
+      </c>
+      <c r="H9" s="15">
+        <v>10</v>
+      </c>
+      <c r="I9" t="s" s="14">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" ht="124" customHeight="1">
+      <c r="A10" t="s" s="12">
+        <v>52</v>
+      </c>
+      <c r="B10" t="s" s="13">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s" s="14">
+        <v>53</v>
+      </c>
+      <c r="D10" s="15">
+        <v>5</v>
+      </c>
+      <c r="E10" s="15">
         <v>9</v>
       </c>
-      <c r="B2" t="s" s="4">
+      <c r="F10" t="s" s="14">
+        <v>54</v>
+      </c>
+      <c r="G10" t="s" s="14">
+        <v>55</v>
+      </c>
+      <c r="H10" s="15">
         <v>10</v>
       </c>
-      <c r="C2" t="s" s="5">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s" s="5">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s" s="5">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s" s="5">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s" s="5">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s" s="5">
+      <c r="I10" t="s" s="14">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" ht="112" customHeight="1">
+      <c r="A11" t="s" s="12">
+        <v>57</v>
+      </c>
+      <c r="B11" t="s" s="13">
         <v>16</v>
       </c>
-      <c r="I2" t="s" s="5">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" ht="32.05" customHeight="1">
-      <c r="A3" t="s" s="6">
-        <v>18</v>
-      </c>
-      <c r="B3" t="s" s="7">
+      <c r="C11" t="s" s="14">
+        <v>58</v>
+      </c>
+      <c r="D11" s="15">
+        <v>5</v>
+      </c>
+      <c r="E11" s="15">
         <v>10</v>
       </c>
-      <c r="C3" t="s" s="8">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s" s="8">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s" s="8">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s" s="8">
-        <v>21</v>
-      </c>
-      <c r="G3" t="s" s="8">
-        <v>22</v>
-      </c>
-      <c r="H3" t="s" s="8">
-        <v>23</v>
-      </c>
-      <c r="I3" t="s" s="8">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" ht="32.05" customHeight="1">
-      <c r="A4" t="s" s="6">
-        <v>25</v>
-      </c>
-      <c r="B4" t="s" s="7">
+      <c r="F11" t="s" s="14">
+        <v>59</v>
+      </c>
+      <c r="G11" t="s" s="14">
+        <v>60</v>
+      </c>
+      <c r="H11" s="15">
         <v>10</v>
       </c>
-      <c r="C4" t="s" s="8">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s" s="8">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s" s="8">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s" s="8">
-        <v>27</v>
-      </c>
-      <c r="G4" t="s" s="8">
-        <v>28</v>
-      </c>
-      <c r="H4" t="s" s="8">
-        <v>29</v>
-      </c>
-      <c r="I4" t="s" s="8">
+      <c r="I11" t="s" s="14">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" ht="172" customHeight="1">
+      <c r="A12" t="s" s="16">
+        <v>61</v>
+      </c>
+      <c r="B12" t="s" s="17">
+        <v>62</v>
+      </c>
+      <c r="C12" t="s" s="18">
+        <v>63</v>
+      </c>
+      <c r="D12" s="19">
+        <v>1</v>
+      </c>
+      <c r="E12" s="19">
+        <v>1</v>
+      </c>
+      <c r="F12" t="s" s="18">
+        <v>64</v>
+      </c>
+      <c r="G12" t="s" s="18">
+        <v>65</v>
+      </c>
+      <c r="H12" s="19">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" ht="32.05" customHeight="1">
-      <c r="A5" t="s" s="6">
-        <v>31</v>
-      </c>
-      <c r="B5" t="s" s="7">
+      <c r="I12" t="s" s="18">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" ht="172" customHeight="1">
+      <c r="A13" t="s" s="16">
+        <v>67</v>
+      </c>
+      <c r="B13" t="s" s="17">
+        <v>62</v>
+      </c>
+      <c r="C13" t="s" s="18">
+        <v>68</v>
+      </c>
+      <c r="D13" s="19">
+        <v>2</v>
+      </c>
+      <c r="E13" s="19">
+        <v>2</v>
+      </c>
+      <c r="F13" t="s" s="18">
+        <v>69</v>
+      </c>
+      <c r="G13" t="s" s="18">
+        <v>70</v>
+      </c>
+      <c r="H13" s="19">
+        <v>30</v>
+      </c>
+      <c r="I13" t="s" s="18">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" ht="124" customHeight="1">
+      <c r="A14" t="s" s="16">
+        <v>72</v>
+      </c>
+      <c r="B14" t="s" s="17">
+        <v>62</v>
+      </c>
+      <c r="C14" t="s" s="18">
+        <v>73</v>
+      </c>
+      <c r="D14" s="19">
+        <v>3</v>
+      </c>
+      <c r="E14" s="19">
+        <v>3</v>
+      </c>
+      <c r="F14" t="s" s="18">
+        <v>74</v>
+      </c>
+      <c r="G14" t="s" s="18">
+        <v>75</v>
+      </c>
+      <c r="H14" s="19">
+        <v>30</v>
+      </c>
+      <c r="I14" t="s" s="18">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" ht="148" customHeight="1">
+      <c r="A15" t="s" s="16">
+        <v>77</v>
+      </c>
+      <c r="B15" t="s" s="17">
+        <v>62</v>
+      </c>
+      <c r="C15" t="s" s="18">
+        <v>78</v>
+      </c>
+      <c r="D15" s="19">
+        <v>4</v>
+      </c>
+      <c r="E15" s="19">
+        <v>4</v>
+      </c>
+      <c r="F15" t="s" s="18">
+        <v>79</v>
+      </c>
+      <c r="G15" t="s" s="18">
+        <v>80</v>
+      </c>
+      <c r="H15" s="19">
+        <v>30</v>
+      </c>
+      <c r="I15" t="s" s="18">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" ht="136" customHeight="1">
+      <c r="A16" t="s" s="16">
+        <v>82</v>
+      </c>
+      <c r="B16" t="s" s="17">
+        <v>62</v>
+      </c>
+      <c r="C16" t="s" s="18">
+        <v>83</v>
+      </c>
+      <c r="D16" s="19">
+        <v>4</v>
+      </c>
+      <c r="E16" s="19">
+        <v>5</v>
+      </c>
+      <c r="F16" t="s" s="18">
+        <v>84</v>
+      </c>
+      <c r="G16" t="s" s="18">
+        <v>85</v>
+      </c>
+      <c r="H16" s="19">
+        <v>30</v>
+      </c>
+      <c r="I16" t="s" s="18">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" ht="148" customHeight="1">
+      <c r="A17" t="s" s="16">
+        <v>87</v>
+      </c>
+      <c r="B17" t="s" s="17">
+        <v>62</v>
+      </c>
+      <c r="C17" t="s" s="18">
+        <v>88</v>
+      </c>
+      <c r="D17" s="19">
+        <v>5</v>
+      </c>
+      <c r="E17" s="19">
+        <v>6</v>
+      </c>
+      <c r="F17" t="s" s="18">
+        <v>89</v>
+      </c>
+      <c r="G17" t="s" s="18">
+        <v>90</v>
+      </c>
+      <c r="H17" s="19">
+        <v>30</v>
+      </c>
+      <c r="I17" t="s" s="18">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" ht="136" customHeight="1">
+      <c r="A18" t="s" s="16">
+        <v>92</v>
+      </c>
+      <c r="B18" t="s" s="17">
+        <v>62</v>
+      </c>
+      <c r="C18" t="s" s="18">
+        <v>93</v>
+      </c>
+      <c r="D18" s="19">
+        <v>6</v>
+      </c>
+      <c r="E18" s="19">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s" s="18">
+        <v>94</v>
+      </c>
+      <c r="G18" t="s" s="18">
+        <v>95</v>
+      </c>
+      <c r="H18" s="19">
+        <v>30</v>
+      </c>
+      <c r="I18" t="s" s="18">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" ht="124" customHeight="1">
+      <c r="A19" t="s" s="16">
+        <v>97</v>
+      </c>
+      <c r="B19" t="s" s="17">
+        <v>62</v>
+      </c>
+      <c r="C19" t="s" s="18">
+        <v>98</v>
+      </c>
+      <c r="D19" s="19">
+        <v>7</v>
+      </c>
+      <c r="E19" s="19">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s" s="18">
+        <v>99</v>
+      </c>
+      <c r="G19" t="s" s="18">
+        <v>100</v>
+      </c>
+      <c r="H19" s="19">
+        <v>30</v>
+      </c>
+      <c r="I19" t="s" s="18">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" ht="148" customHeight="1">
+      <c r="A20" t="s" s="16">
+        <v>102</v>
+      </c>
+      <c r="B20" t="s" s="17">
+        <v>62</v>
+      </c>
+      <c r="C20" t="s" s="18">
+        <v>103</v>
+      </c>
+      <c r="D20" s="19">
+        <v>8</v>
+      </c>
+      <c r="E20" s="19">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s" s="18">
+        <v>104</v>
+      </c>
+      <c r="G20" t="s" s="18">
+        <v>105</v>
+      </c>
+      <c r="H20" s="19">
+        <v>30</v>
+      </c>
+      <c r="I20" t="s" s="18">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" ht="124" customHeight="1">
+      <c r="A21" t="s" s="16">
+        <v>107</v>
+      </c>
+      <c r="B21" t="s" s="17">
+        <v>62</v>
+      </c>
+      <c r="C21" t="s" s="18">
+        <v>108</v>
+      </c>
+      <c r="D21" s="19">
+        <v>9</v>
+      </c>
+      <c r="E21" s="19">
         <v>10</v>
       </c>
-      <c r="C5" t="s" s="8">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s" s="8">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s" s="8">
-        <v>33</v>
-      </c>
-      <c r="F5" t="s" s="8">
-        <v>34</v>
-      </c>
-      <c r="G5" t="s" s="8">
-        <v>35</v>
-      </c>
-      <c r="H5" t="s" s="8">
-        <v>36</v>
-      </c>
-      <c r="I5" t="s" s="8">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" ht="20.05" customHeight="1">
-      <c r="A6" t="s" s="6">
-        <v>38</v>
-      </c>
-      <c r="B6" t="s" s="7">
+      <c r="F21" t="s" s="18">
+        <v>109</v>
+      </c>
+      <c r="G21" t="s" s="18">
+        <v>110</v>
+      </c>
+      <c r="H21" s="19">
+        <v>30</v>
+      </c>
+      <c r="I21" t="s" s="18">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" ht="160" customHeight="1">
+      <c r="A22" t="s" s="20">
+        <v>112</v>
+      </c>
+      <c r="B22" t="s" s="21">
+        <v>113</v>
+      </c>
+      <c r="C22" t="s" s="22">
+        <v>114</v>
+      </c>
+      <c r="D22" s="23">
+        <v>1</v>
+      </c>
+      <c r="E22" t="s" s="22">
+        <v>115</v>
+      </c>
+      <c r="F22" t="s" s="22">
+        <v>116</v>
+      </c>
+      <c r="G22" t="s" s="22">
+        <v>117</v>
+      </c>
+      <c r="H22" s="23">
         <v>10</v>
       </c>
-      <c r="C6" t="s" s="8">
-        <v>39</v>
-      </c>
-      <c r="D6" t="s" s="8">
-        <v>33</v>
-      </c>
-      <c r="E6" t="s" s="8">
-        <v>40</v>
-      </c>
-      <c r="F6" t="s" s="8">
-        <v>41</v>
-      </c>
-      <c r="G6" t="s" s="8">
-        <v>42</v>
-      </c>
-      <c r="H6" t="s" s="8">
-        <v>43</v>
-      </c>
-      <c r="I6" t="s" s="8">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" ht="32.05" customHeight="1">
-      <c r="A7" t="s" s="6">
-        <v>45</v>
-      </c>
-      <c r="B7" t="s" s="7">
-        <v>46</v>
-      </c>
-      <c r="C7" t="s" s="8">
-        <v>47</v>
-      </c>
-      <c r="D7" t="s" s="8">
-        <v>40</v>
-      </c>
-      <c r="E7" t="s" s="8">
-        <v>20</v>
-      </c>
-      <c r="F7" t="s" s="8">
-        <v>48</v>
-      </c>
-      <c r="G7" t="s" s="8">
-        <v>49</v>
-      </c>
-      <c r="H7" t="s" s="8">
+      <c r="I22" t="s" s="22">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" ht="136" customHeight="1">
+      <c r="A23" t="s" s="24">
+        <v>119</v>
+      </c>
+      <c r="B23" t="s" s="25">
+        <v>120</v>
+      </c>
+      <c r="C23" t="s" s="26">
+        <v>121</v>
+      </c>
+      <c r="D23" s="27">
+        <v>3</v>
+      </c>
+      <c r="E23" s="27">
+        <v>1</v>
+      </c>
+      <c r="F23" t="s" s="26">
+        <v>122</v>
+      </c>
+      <c r="G23" t="s" s="26">
+        <v>123</v>
+      </c>
+      <c r="H23" s="27">
         <v>50</v>
       </c>
-      <c r="I7" t="s" s="8">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" ht="32.05" customHeight="1">
-      <c r="A8" t="s" s="6">
-        <v>52</v>
-      </c>
-      <c r="B8" t="s" s="7">
-        <v>46</v>
-      </c>
-      <c r="C8" t="s" s="8">
-        <v>53</v>
-      </c>
-      <c r="D8" t="s" s="8">
-        <v>33</v>
-      </c>
-      <c r="E8" t="s" s="8">
-        <v>13</v>
-      </c>
-      <c r="F8" t="s" s="8">
-        <v>54</v>
-      </c>
-      <c r="G8" t="s" s="8">
-        <v>55</v>
-      </c>
-      <c r="H8" t="s" s="8">
-        <v>56</v>
-      </c>
-      <c r="I8" t="s" s="8">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" ht="32.05" customHeight="1">
-      <c r="A9" t="s" s="6">
-        <v>58</v>
-      </c>
-      <c r="B9" t="s" s="7">
-        <v>46</v>
-      </c>
-      <c r="C9" t="s" s="8">
-        <v>59</v>
-      </c>
-      <c r="D9" t="s" s="8">
-        <v>60</v>
-      </c>
-      <c r="E9" t="s" s="8">
-        <v>40</v>
-      </c>
-      <c r="F9" t="s" s="8">
-        <v>61</v>
-      </c>
-      <c r="G9" t="s" s="8">
-        <v>62</v>
-      </c>
-      <c r="H9" t="s" s="8">
-        <v>63</v>
-      </c>
-      <c r="I9" t="s" s="8">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" ht="44.05" customHeight="1">
-      <c r="A10" t="s" s="6">
-        <v>65</v>
-      </c>
-      <c r="B10" t="s" s="7">
-        <v>46</v>
-      </c>
-      <c r="C10" t="s" s="8">
-        <v>66</v>
-      </c>
-      <c r="D10" t="s" s="8">
-        <v>67</v>
-      </c>
-      <c r="E10" t="s" s="8">
-        <v>33</v>
-      </c>
-      <c r="F10" t="s" s="8">
-        <v>68</v>
-      </c>
-      <c r="G10" t="s" s="8">
-        <v>69</v>
-      </c>
-      <c r="H10" t="s" s="8">
-        <v>70</v>
-      </c>
-      <c r="I10" t="s" s="8">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" ht="32.05" customHeight="1">
-      <c r="A11" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="B11" t="s" s="7">
-        <v>46</v>
-      </c>
-      <c r="C11" t="s" s="8">
-        <v>73</v>
-      </c>
-      <c r="D11" t="s" s="8">
-        <v>74</v>
-      </c>
-      <c r="E11" t="s" s="8">
-        <v>60</v>
-      </c>
-      <c r="F11" t="s" s="8">
-        <v>75</v>
-      </c>
-      <c r="G11" t="s" s="8">
-        <v>76</v>
-      </c>
-      <c r="H11" t="s" s="8">
-        <v>77</v>
-      </c>
-      <c r="I11" t="s" s="8">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="12" ht="32.05" customHeight="1">
-      <c r="A12" t="s" s="6">
-        <v>79</v>
-      </c>
-      <c r="B12" t="s" s="7">
-        <v>80</v>
-      </c>
-      <c r="C12" t="s" s="8">
-        <v>81</v>
-      </c>
-      <c r="D12" t="s" s="8">
-        <v>40</v>
-      </c>
-      <c r="E12" t="s" s="8">
-        <v>82</v>
-      </c>
-      <c r="F12" t="s" s="8">
-        <v>83</v>
-      </c>
-      <c r="G12" t="s" s="8">
-        <v>84</v>
-      </c>
-      <c r="H12" t="s" s="8">
-        <v>85</v>
-      </c>
-      <c r="I12" t="s" s="8">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="13" ht="44.05" customHeight="1">
-      <c r="A13" t="s" s="6">
-        <v>87</v>
-      </c>
-      <c r="B13" t="s" s="7">
-        <v>80</v>
-      </c>
-      <c r="C13" t="s" s="8">
-        <v>88</v>
-      </c>
-      <c r="D13" t="s" s="8">
-        <v>33</v>
-      </c>
-      <c r="E13" t="s" s="8">
-        <v>74</v>
-      </c>
-      <c r="F13" t="s" s="8">
-        <v>89</v>
-      </c>
-      <c r="G13" t="s" s="8">
-        <v>90</v>
-      </c>
-      <c r="H13" t="s" s="8">
-        <v>91</v>
-      </c>
-      <c r="I13" t="s" s="8">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" ht="32.05" customHeight="1">
-      <c r="A14" t="s" s="6">
-        <v>93</v>
-      </c>
-      <c r="B14" t="s" s="7">
-        <v>80</v>
-      </c>
-      <c r="C14" t="s" s="8">
-        <v>94</v>
-      </c>
-      <c r="D14" t="s" s="8">
-        <v>60</v>
-      </c>
-      <c r="E14" t="s" s="8">
-        <v>95</v>
-      </c>
-      <c r="F14" t="s" s="8">
-        <v>96</v>
-      </c>
-      <c r="G14" t="s" s="8">
-        <v>97</v>
-      </c>
-      <c r="H14" t="s" s="8">
-        <v>98</v>
-      </c>
-      <c r="I14" t="s" s="8">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="15" ht="32.05" customHeight="1">
-      <c r="A15" t="s" s="6">
-        <v>100</v>
-      </c>
-      <c r="B15" t="s" s="7">
-        <v>101</v>
-      </c>
-      <c r="C15" t="s" s="8">
-        <v>102</v>
-      </c>
-      <c r="D15" t="s" s="8">
-        <v>82</v>
-      </c>
-      <c r="E15" t="s" s="8">
-        <v>103</v>
-      </c>
-      <c r="F15" t="s" s="8">
-        <v>104</v>
-      </c>
-      <c r="G15" t="s" s="8">
-        <v>105</v>
-      </c>
-      <c r="H15" t="s" s="8">
-        <v>95</v>
-      </c>
-      <c r="I15" t="s" s="8">
-        <v>106</v>
+      <c r="I23" t="s" s="26">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" ht="136" customHeight="1">
+      <c r="A24" t="s" s="24">
+        <v>125</v>
+      </c>
+      <c r="B24" t="s" s="25">
+        <v>120</v>
+      </c>
+      <c r="C24" t="s" s="26">
+        <v>126</v>
+      </c>
+      <c r="D24" s="27">
+        <v>7</v>
+      </c>
+      <c r="E24" s="27">
+        <v>2</v>
+      </c>
+      <c r="F24" t="s" s="26">
+        <v>127</v>
+      </c>
+      <c r="G24" t="s" s="26">
+        <v>128</v>
+      </c>
+      <c r="H24" s="27">
+        <v>50</v>
+      </c>
+      <c r="I24" t="s" s="26">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="25" ht="136" customHeight="1">
+      <c r="A25" t="s" s="24">
+        <v>130</v>
+      </c>
+      <c r="B25" t="s" s="25">
+        <v>120</v>
+      </c>
+      <c r="C25" t="s" s="26">
+        <v>131</v>
+      </c>
+      <c r="D25" s="27">
+        <v>10</v>
+      </c>
+      <c r="E25" s="27">
+        <v>3</v>
+      </c>
+      <c r="F25" t="s" s="26">
+        <v>132</v>
+      </c>
+      <c r="G25" t="s" s="26">
+        <v>133</v>
+      </c>
+      <c r="H25" s="27">
+        <v>50</v>
+      </c>
+      <c r="I25" t="s" s="26">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2024,4 +2973,1824 @@
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:B9"/>
+  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="22.8125" style="28" customWidth="1"/>
+    <col min="2" max="2" width="30.7422" style="28" customWidth="1"/>
+    <col min="3" max="16384" width="16.3516" style="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27.65" customHeight="1">
+      <c r="A1" t="s" s="29">
+        <v>136</v>
+      </c>
+      <c r="B1" s="29"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
+      <c r="A2" t="s" s="30">
+        <v>138</v>
+      </c>
+      <c r="B2" t="s" s="30">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" ht="20.25" customHeight="1">
+      <c r="A3" t="s" s="31">
+        <v>140</v>
+      </c>
+      <c r="B3" s="32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" ht="20.05" customHeight="1">
+      <c r="A4" t="s" s="33">
+        <v>141</v>
+      </c>
+      <c r="B4" s="34">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" ht="20.05" customHeight="1">
+      <c r="A5" t="s" s="33">
+        <v>142</v>
+      </c>
+      <c r="B5" s="34">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" ht="20.05" customHeight="1">
+      <c r="A6" t="s" s="33">
+        <v>143</v>
+      </c>
+      <c r="B6" s="34" cm="1">
+        <f t="array" ref="B6">(B5-B4)/B9</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" ht="20.05" customHeight="1">
+      <c r="A7" t="s" s="33">
+        <v>144</v>
+      </c>
+      <c r="B7" s="34">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" ht="32.05" customHeight="1">
+      <c r="A8" t="s" s="33">
+        <v>145</v>
+      </c>
+      <c r="B8" s="34">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" ht="32.05" customHeight="1">
+      <c r="A9" t="s" s="33">
+        <v>146</v>
+      </c>
+      <c r="B9" s="34">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:G13"/>
+  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="5" width="16.3516" style="35" customWidth="1"/>
+    <col min="6" max="6" width="18.4141" style="35" customWidth="1"/>
+    <col min="7" max="7" width="16.3516" style="35" customWidth="1"/>
+    <col min="8" max="16384" width="16.3516" style="35" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27.65" customHeight="1">
+      <c r="A1" t="s" s="29">
+        <v>147</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+    </row>
+    <row r="2" ht="32.25" customHeight="1">
+      <c r="A2" t="s" s="36">
+        <v>149</v>
+      </c>
+      <c r="B2" t="s" s="36">
+        <v>115</v>
+      </c>
+      <c r="C2" t="s" s="36">
+        <v>150</v>
+      </c>
+      <c r="D2" t="s" s="36">
+        <v>151</v>
+      </c>
+      <c r="E2" t="s" s="36">
+        <v>152</v>
+      </c>
+      <c r="F2" t="s" s="36">
+        <v>153</v>
+      </c>
+      <c r="G2" s="37"/>
+    </row>
+    <row r="3" ht="20.25" customHeight="1">
+      <c r="A3" s="38">
+        <v>1</v>
+      </c>
+      <c r="B3" s="39"/>
+      <c r="C3" t="s" s="40">
+        <v>154</v>
+      </c>
+      <c r="D3" s="41" cm="1">
+        <f t="array" ref="D3">F3/'Sheet 2 - Базовые переменные'!$B$7*VLOOKUP(C3,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>0.52</v>
+      </c>
+      <c r="E3" s="42">
+        <v>1</v>
+      </c>
+      <c r="F3" s="41" cm="1">
+        <f t="array" ref="F3">AVERAGE('Sheet 2 - Базовые переменные'!$B$8:$B$9)*E3*'Sheet 2 - Базовые переменные'!$B$7*'Sheet 2 - Базовые переменные'!$B$7*VLOOKUP(C3,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>20.8</v>
+      </c>
+      <c r="G3" s="43"/>
+    </row>
+    <row r="4" ht="20.05" customHeight="1">
+      <c r="A4" s="44">
+        <v>2</v>
+      </c>
+      <c r="B4" s="45"/>
+      <c r="C4" t="s" s="46">
+        <v>154</v>
+      </c>
+      <c r="D4" s="47" cm="1">
+        <f t="array" ref="D4">F4/'Sheet 2 - Базовые переменные'!$B$7*VLOOKUP(C4,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>1.04</v>
+      </c>
+      <c r="E4" s="48">
+        <v>2</v>
+      </c>
+      <c r="F4" s="47" cm="1">
+        <f t="array" ref="F4">AVERAGE('Sheet 2 - Базовые переменные'!$B$8:$B$9)*E4*'Sheet 2 - Базовые переменные'!$B$7*'Sheet 2 - Базовые переменные'!$B$7*VLOOKUP(C4,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>41.6</v>
+      </c>
+      <c r="G4" s="49"/>
+    </row>
+    <row r="5" ht="20.05" customHeight="1">
+      <c r="A5" s="44">
+        <v>3</v>
+      </c>
+      <c r="B5" s="45"/>
+      <c r="C5" t="s" s="46">
+        <v>154</v>
+      </c>
+      <c r="D5" s="47" cm="1">
+        <f t="array" ref="D5">F5/'Sheet 2 - Базовые переменные'!$B$7*VLOOKUP(C5,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>1.56</v>
+      </c>
+      <c r="E5" s="48">
+        <v>3</v>
+      </c>
+      <c r="F5" s="47" cm="1">
+        <f t="array" ref="F5">AVERAGE('Sheet 2 - Базовые переменные'!$B$8:$B$9)*E5*'Sheet 2 - Базовые переменные'!$B$7*'Sheet 2 - Базовые переменные'!$B$7*VLOOKUP(C5,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>62.4</v>
+      </c>
+      <c r="G5" s="49"/>
+    </row>
+    <row r="6" ht="20.05" customHeight="1">
+      <c r="A6" s="44">
+        <v>4</v>
+      </c>
+      <c r="B6" s="45"/>
+      <c r="C6" t="s" s="46">
+        <v>154</v>
+      </c>
+      <c r="D6" s="47" cm="1">
+        <f t="array" ref="D6">F6/'Sheet 2 - Базовые переменные'!$B$7*VLOOKUP(C6,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>2.08</v>
+      </c>
+      <c r="E6" s="48">
+        <v>4</v>
+      </c>
+      <c r="F6" s="47" cm="1">
+        <f t="array" ref="F6">AVERAGE('Sheet 2 - Базовые переменные'!$B$8:$B$9)*E6*'Sheet 2 - Базовые переменные'!$B$7*'Sheet 2 - Базовые переменные'!$B$7*VLOOKUP(C6,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>83.2</v>
+      </c>
+      <c r="G6" s="49"/>
+    </row>
+    <row r="7" ht="20.05" customHeight="1">
+      <c r="A7" s="44">
+        <v>5</v>
+      </c>
+      <c r="B7" s="45"/>
+      <c r="C7" t="s" s="46">
+        <v>154</v>
+      </c>
+      <c r="D7" s="47" cm="1">
+        <f t="array" ref="D7">F7/'Sheet 2 - Базовые переменные'!$B$7*VLOOKUP(C7,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>2.6</v>
+      </c>
+      <c r="E7" s="48">
+        <v>5</v>
+      </c>
+      <c r="F7" s="47" cm="1">
+        <f t="array" ref="F7">AVERAGE('Sheet 2 - Базовые переменные'!$B$8:$B$9)*E7*'Sheet 2 - Базовые переменные'!$B$7*'Sheet 2 - Базовые переменные'!$B$7*VLOOKUP(C7,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>104</v>
+      </c>
+      <c r="G7" s="49"/>
+    </row>
+    <row r="8" ht="20.05" customHeight="1">
+      <c r="A8" s="44">
+        <v>6</v>
+      </c>
+      <c r="B8" s="45"/>
+      <c r="C8" t="s" s="46">
+        <v>154</v>
+      </c>
+      <c r="D8" s="47" cm="1">
+        <f t="array" ref="D8">F8/'Sheet 2 - Базовые переменные'!$B$7*VLOOKUP(C8,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>3.12</v>
+      </c>
+      <c r="E8" s="48">
+        <v>6</v>
+      </c>
+      <c r="F8" s="47" cm="1">
+        <f t="array" ref="F8">AVERAGE('Sheet 2 - Базовые переменные'!$B$8:$B$9)*E8*'Sheet 2 - Базовые переменные'!$B$7*'Sheet 2 - Базовые переменные'!$B$7*VLOOKUP(C8,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>124.8</v>
+      </c>
+      <c r="G8" s="49"/>
+    </row>
+    <row r="9" ht="20.05" customHeight="1">
+      <c r="A9" s="44">
+        <v>7</v>
+      </c>
+      <c r="B9" s="45"/>
+      <c r="C9" t="s" s="46">
+        <v>154</v>
+      </c>
+      <c r="D9" s="47" cm="1">
+        <f t="array" ref="D9">F9/'Sheet 2 - Базовые переменные'!$B$7*VLOOKUP(C9,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>3.64</v>
+      </c>
+      <c r="E9" s="48">
+        <v>7</v>
+      </c>
+      <c r="F9" s="47" cm="1">
+        <f t="array" ref="F9">AVERAGE('Sheet 2 - Базовые переменные'!$B$8:$B$9)*E9*'Sheet 2 - Базовые переменные'!$B$7*'Sheet 2 - Базовые переменные'!$B$7*VLOOKUP(C9,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>145.6</v>
+      </c>
+      <c r="G9" s="49"/>
+    </row>
+    <row r="10" ht="20.05" customHeight="1">
+      <c r="A10" s="44">
+        <v>8</v>
+      </c>
+      <c r="B10" s="45"/>
+      <c r="C10" t="s" s="46">
+        <v>154</v>
+      </c>
+      <c r="D10" s="47" cm="1">
+        <f t="array" ref="D10">F10/'Sheet 2 - Базовые переменные'!$B$7*VLOOKUP(C10,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>4.16</v>
+      </c>
+      <c r="E10" s="48">
+        <v>8</v>
+      </c>
+      <c r="F10" s="47" cm="1">
+        <f t="array" ref="F10">AVERAGE('Sheet 2 - Базовые переменные'!$B$8:$B$9)*E10*'Sheet 2 - Базовые переменные'!$B$7*'Sheet 2 - Базовые переменные'!$B$7*VLOOKUP(C10,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>166.4</v>
+      </c>
+      <c r="G10" s="49"/>
+    </row>
+    <row r="11" ht="20.05" customHeight="1">
+      <c r="A11" s="44">
+        <v>9</v>
+      </c>
+      <c r="B11" s="45"/>
+      <c r="C11" t="s" s="46">
+        <v>154</v>
+      </c>
+      <c r="D11" s="47" cm="1">
+        <f t="array" ref="D11">F11/'Sheet 2 - Базовые переменные'!$B$7*VLOOKUP(C11,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>4.68</v>
+      </c>
+      <c r="E11" s="48">
+        <v>9</v>
+      </c>
+      <c r="F11" s="47" cm="1">
+        <f t="array" ref="F11">AVERAGE('Sheet 2 - Базовые переменные'!$B$8:$B$9)*E11*'Sheet 2 - Базовые переменные'!$B$7*'Sheet 2 - Базовые переменные'!$B$7*VLOOKUP(C11,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>187.2</v>
+      </c>
+      <c r="G11" s="49"/>
+    </row>
+    <row r="12" ht="20.05" customHeight="1">
+      <c r="A12" s="44">
+        <v>10</v>
+      </c>
+      <c r="B12" s="45"/>
+      <c r="C12" t="s" s="46">
+        <v>154</v>
+      </c>
+      <c r="D12" s="47" cm="1">
+        <f t="array" ref="D12">F12/'Sheet 2 - Базовые переменные'!$B$7*VLOOKUP(C12,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>5.2</v>
+      </c>
+      <c r="E12" s="48">
+        <v>10</v>
+      </c>
+      <c r="F12" s="47" cm="1">
+        <f t="array" ref="F12">AVERAGE('Sheet 2 - Базовые переменные'!$B$8:$B$9)*E12*'Sheet 2 - Базовые переменные'!$B$7*'Sheet 2 - Базовые переменные'!$B$7*VLOOKUP(C12,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>208</v>
+      </c>
+      <c r="G12" s="49"/>
+    </row>
+    <row r="13" ht="32.05" customHeight="1">
+      <c r="A13" s="50"/>
+      <c r="B13" t="s" s="51">
+        <v>155</v>
+      </c>
+      <c r="C13" s="46"/>
+      <c r="D13" s="47" cm="1">
+        <f t="array" ref="D13">AVERAGE(D3:D12)</f>
+        <v>2.86</v>
+      </c>
+      <c r="E13" s="49"/>
+      <c r="F13" s="47" cm="1">
+        <f t="array" ref="F13">AVERAGE(F3:F12)/AVERAGE('Sheet 2 - Базовые переменные'!B8:B9)</f>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G13" s="49"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C12">
+      <formula1>"Синий,Красный,Фиолетовый,Золотой"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:G13"/>
+  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="5" width="16.3516" style="52" customWidth="1"/>
+    <col min="6" max="6" width="18.4141" style="52" customWidth="1"/>
+    <col min="7" max="7" width="16.3516" style="52" customWidth="1"/>
+    <col min="8" max="16384" width="16.3516" style="52" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27.65" customHeight="1">
+      <c r="A1" t="s" s="29">
+        <v>156</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+    </row>
+    <row r="2" ht="32.25" customHeight="1">
+      <c r="A2" t="s" s="36">
+        <v>149</v>
+      </c>
+      <c r="B2" t="s" s="36">
+        <v>115</v>
+      </c>
+      <c r="C2" t="s" s="36">
+        <v>150</v>
+      </c>
+      <c r="D2" t="s" s="36">
+        <v>151</v>
+      </c>
+      <c r="E2" t="s" s="36">
+        <v>152</v>
+      </c>
+      <c r="F2" t="s" s="36">
+        <v>153</v>
+      </c>
+      <c r="G2" s="37"/>
+    </row>
+    <row r="3" ht="20.25" customHeight="1">
+      <c r="A3" s="38">
+        <v>1</v>
+      </c>
+      <c r="B3" s="39"/>
+      <c r="C3" t="s" s="40">
+        <v>158</v>
+      </c>
+      <c r="D3" s="41" cm="1">
+        <f t="array" ref="D3">F3/'Sheet 2 - Базовые переменные'!$B$7*-1*VLOOKUP(C3,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>0.8774999999999999</v>
+      </c>
+      <c r="E3" s="42">
+        <v>1</v>
+      </c>
+      <c r="F3" s="41" cm="1">
+        <f t="array" ref="F3">AVERAGE('Sheet 2 - Базовые переменные'!$B$8:$B$9)*E3*(-'Sheet 2 - Базовые переменные'!$B$7+1)*VLOOKUP(C3,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>-11.7</v>
+      </c>
+      <c r="G3" s="43"/>
+    </row>
+    <row r="4" ht="20.05" customHeight="1">
+      <c r="A4" s="44">
+        <v>2</v>
+      </c>
+      <c r="B4" s="45"/>
+      <c r="C4" t="s" s="46">
+        <v>158</v>
+      </c>
+      <c r="D4" s="47" cm="1">
+        <f t="array" ref="D4">F4/'Sheet 2 - Базовые переменные'!$B$7*-1*VLOOKUP(C4,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>1.755</v>
+      </c>
+      <c r="E4" s="48">
+        <v>2</v>
+      </c>
+      <c r="F4" s="47" cm="1">
+        <f t="array" ref="F4">AVERAGE('Sheet 2 - Базовые переменные'!$B$8:$B$9)*E4*(-'Sheet 2 - Базовые переменные'!$B$7+1)*VLOOKUP(C4,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>-23.4</v>
+      </c>
+      <c r="G4" s="49"/>
+    </row>
+    <row r="5" ht="20.05" customHeight="1">
+      <c r="A5" s="44">
+        <v>3</v>
+      </c>
+      <c r="B5" s="45"/>
+      <c r="C5" t="s" s="46">
+        <v>158</v>
+      </c>
+      <c r="D5" s="47" cm="1">
+        <f t="array" ref="D5">F5/'Sheet 2 - Базовые переменные'!$B$7*-1*VLOOKUP(C5,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>2.6325</v>
+      </c>
+      <c r="E5" s="48">
+        <v>3</v>
+      </c>
+      <c r="F5" s="47" cm="1">
+        <f t="array" ref="F5">AVERAGE('Sheet 2 - Базовые переменные'!$B$8:$B$9)*E5*(-'Sheet 2 - Базовые переменные'!$B$7+1)*VLOOKUP(C5,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>-35.1</v>
+      </c>
+      <c r="G5" s="49"/>
+    </row>
+    <row r="6" ht="20.05" customHeight="1">
+      <c r="A6" s="44">
+        <v>4</v>
+      </c>
+      <c r="B6" s="45"/>
+      <c r="C6" t="s" s="46">
+        <v>158</v>
+      </c>
+      <c r="D6" s="47" cm="1">
+        <f t="array" ref="D6">F6/'Sheet 2 - Базовые переменные'!$B$7*-1*VLOOKUP(C6,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>3.51</v>
+      </c>
+      <c r="E6" s="48">
+        <v>4</v>
+      </c>
+      <c r="F6" s="47" cm="1">
+        <f t="array" ref="F6">AVERAGE('Sheet 2 - Базовые переменные'!$B$8:$B$9)*E6*(-'Sheet 2 - Базовые переменные'!$B$7+1)*VLOOKUP(C6,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>-46.8</v>
+      </c>
+      <c r="G6" s="49"/>
+    </row>
+    <row r="7" ht="20.05" customHeight="1">
+      <c r="A7" s="44">
+        <v>5</v>
+      </c>
+      <c r="B7" s="45"/>
+      <c r="C7" t="s" s="46">
+        <v>158</v>
+      </c>
+      <c r="D7" s="47" cm="1">
+        <f t="array" ref="D7">F7/'Sheet 2 - Базовые переменные'!$B$7*-1*VLOOKUP(C7,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>4.3875</v>
+      </c>
+      <c r="E7" s="48">
+        <v>5</v>
+      </c>
+      <c r="F7" s="47" cm="1">
+        <f t="array" ref="F7">AVERAGE('Sheet 2 - Базовые переменные'!$B$8:$B$9)*E7*(-'Sheet 2 - Базовые переменные'!$B$7+1)*VLOOKUP(C7,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>-58.5</v>
+      </c>
+      <c r="G7" s="49"/>
+    </row>
+    <row r="8" ht="20.05" customHeight="1">
+      <c r="A8" s="44">
+        <v>6</v>
+      </c>
+      <c r="B8" s="45"/>
+      <c r="C8" t="s" s="46">
+        <v>158</v>
+      </c>
+      <c r="D8" s="47" cm="1">
+        <f t="array" ref="D8">F8/'Sheet 2 - Базовые переменные'!$B$7*-1*VLOOKUP(C8,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>5.265</v>
+      </c>
+      <c r="E8" s="48">
+        <v>6</v>
+      </c>
+      <c r="F8" s="47" cm="1">
+        <f t="array" ref="F8">AVERAGE('Sheet 2 - Базовые переменные'!$B$8:$B$9)*E8*(-'Sheet 2 - Базовые переменные'!$B$7+1)*VLOOKUP(C8,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>-70.2</v>
+      </c>
+      <c r="G8" s="49"/>
+    </row>
+    <row r="9" ht="20.05" customHeight="1">
+      <c r="A9" s="44">
+        <v>7</v>
+      </c>
+      <c r="B9" s="45"/>
+      <c r="C9" t="s" s="46">
+        <v>158</v>
+      </c>
+      <c r="D9" s="47" cm="1">
+        <f t="array" ref="D9">F9/'Sheet 2 - Базовые переменные'!$B$7*-1*VLOOKUP(C9,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>6.1425</v>
+      </c>
+      <c r="E9" s="48">
+        <v>7</v>
+      </c>
+      <c r="F9" s="47" cm="1">
+        <f t="array" ref="F9">AVERAGE('Sheet 2 - Базовые переменные'!$B$8:$B$9)*E9*(-'Sheet 2 - Базовые переменные'!$B$7+1)*VLOOKUP(C9,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>-81.90000000000001</v>
+      </c>
+      <c r="G9" s="49"/>
+    </row>
+    <row r="10" ht="20.05" customHeight="1">
+      <c r="A10" s="44">
+        <v>8</v>
+      </c>
+      <c r="B10" s="45"/>
+      <c r="C10" t="s" s="46">
+        <v>158</v>
+      </c>
+      <c r="D10" s="47" cm="1">
+        <f t="array" ref="D10">F10/'Sheet 2 - Базовые переменные'!$B$7*-1*VLOOKUP(C10,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>7.02</v>
+      </c>
+      <c r="E10" s="48">
+        <v>8</v>
+      </c>
+      <c r="F10" s="47" cm="1">
+        <f t="array" ref="F10">AVERAGE('Sheet 2 - Базовые переменные'!$B$8:$B$9)*E10*(-'Sheet 2 - Базовые переменные'!$B$7+1)*VLOOKUP(C10,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>-93.59999999999999</v>
+      </c>
+      <c r="G10" s="49"/>
+    </row>
+    <row r="11" ht="20.05" customHeight="1">
+      <c r="A11" s="44">
+        <v>9</v>
+      </c>
+      <c r="B11" s="45"/>
+      <c r="C11" t="s" s="46">
+        <v>158</v>
+      </c>
+      <c r="D11" s="47" cm="1">
+        <f t="array" ref="D11">F11/'Sheet 2 - Базовые переменные'!$B$7*-1*VLOOKUP(C11,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>7.8975</v>
+      </c>
+      <c r="E11" s="48">
+        <v>9</v>
+      </c>
+      <c r="F11" s="47" cm="1">
+        <f t="array" ref="F11">AVERAGE('Sheet 2 - Базовые переменные'!$B$8:$B$9)*E11*(-'Sheet 2 - Базовые переменные'!$B$7+1)*VLOOKUP(C11,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>-105.3</v>
+      </c>
+      <c r="G11" s="49"/>
+    </row>
+    <row r="12" ht="20.05" customHeight="1">
+      <c r="A12" s="44">
+        <v>10</v>
+      </c>
+      <c r="B12" s="45"/>
+      <c r="C12" t="s" s="46">
+        <v>158</v>
+      </c>
+      <c r="D12" s="47" cm="1">
+        <f t="array" ref="D12">F12/'Sheet 2 - Базовые переменные'!$B$7*-1*VLOOKUP(C12,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>8.775</v>
+      </c>
+      <c r="E12" s="48">
+        <v>10</v>
+      </c>
+      <c r="F12" s="47" cm="1">
+        <f t="array" ref="F12">AVERAGE('Sheet 2 - Базовые переменные'!$B$8:$B$9)*E12*(-'Sheet 2 - Базовые переменные'!$B$7+1)*VLOOKUP(C12,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>-117</v>
+      </c>
+      <c r="G12" s="49"/>
+    </row>
+    <row r="13" ht="32.05" customHeight="1">
+      <c r="A13" s="50"/>
+      <c r="B13" t="s" s="51">
+        <v>155</v>
+      </c>
+      <c r="C13" s="46"/>
+      <c r="D13" s="47" cm="1">
+        <f t="array" ref="D13">AVERAGE(D3:D12)</f>
+        <v>4.82625</v>
+      </c>
+      <c r="E13" s="49"/>
+      <c r="F13" s="47" cm="1">
+        <f t="array" ref="F13">AVERAGE(F3:F12)/AVERAGE('Sheet 2 - Базовые переменные'!B8:B9)</f>
+        <v>-4.95</v>
+      </c>
+      <c r="G13" s="49"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C12">
+      <formula1>"Синий,Красный,Фиолетовый,Золотой"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:B6"/>
+  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="2" width="16.3516" style="53" customWidth="1"/>
+    <col min="3" max="16384" width="16.3516" style="53" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27.65" customHeight="1">
+      <c r="A1" t="s" s="29">
+        <v>159</v>
+      </c>
+      <c r="B1" s="29"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
+      <c r="A2" t="s" s="30">
+        <v>150</v>
+      </c>
+      <c r="B2" t="s" s="30">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3" ht="20.25" customHeight="1">
+      <c r="A3" t="s" s="31">
+        <v>154</v>
+      </c>
+      <c r="B3" s="54">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" ht="20.05" customHeight="1">
+      <c r="A4" t="s" s="33">
+        <v>158</v>
+      </c>
+      <c r="B4" s="55">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="5" ht="20.05" customHeight="1">
+      <c r="A5" t="s" s="33">
+        <v>162</v>
+      </c>
+      <c r="B5" s="55">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="6" ht="20.05" customHeight="1">
+      <c r="A6" t="s" s="33">
+        <v>163</v>
+      </c>
+      <c r="B6" s="55">
+        <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A6">
+      <formula1>"Синий,Красный,Фиолетовый,Золотой"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:I23"/>
+  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="9" width="16.3516" style="56" customWidth="1"/>
+    <col min="10" max="16384" width="16.3516" style="56" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27.65" customHeight="1">
+      <c r="A1" t="s" s="29">
+        <v>164</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+    </row>
+    <row r="2" ht="20.05" customHeight="1">
+      <c r="A2" s="57"/>
+      <c r="B2" s="57"/>
+      <c r="C2" t="s" s="58">
+        <v>166</v>
+      </c>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="57"/>
+    </row>
+    <row r="3" ht="44.25" customHeight="1">
+      <c r="A3" t="s" s="30">
+        <v>167</v>
+      </c>
+      <c r="B3" t="s" s="30">
+        <v>168</v>
+      </c>
+      <c r="C3" t="str" s="61" cm="1">
+        <f t="array" ref="C3">'Sheet 2 - Вероятность выпадения'!$A3</f>
+        <v>Синий</v>
+      </c>
+      <c r="D3" t="str" s="61" cm="1">
+        <f t="array" ref="D3">'Sheet 2 - Вероятность выпадения'!$A4</f>
+        <v>Красный</v>
+      </c>
+      <c r="E3" t="str" s="61" cm="1">
+        <f t="array" ref="E3">'Sheet 2 - Вероятность выпадения'!$A5</f>
+        <v>Фиолетовый</v>
+      </c>
+      <c r="F3" t="str" s="61" cm="1">
+        <f t="array" ref="F3">'Sheet 2 - Вероятность выпадения'!$A6</f>
+        <v>Золотой</v>
+      </c>
+      <c r="G3" t="s" s="30">
+        <v>173</v>
+      </c>
+      <c r="H3" t="s" s="30">
+        <v>174</v>
+      </c>
+      <c r="I3" t="s" s="30">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" ht="20.25" customHeight="1">
+      <c r="A4" s="62">
+        <v>1</v>
+      </c>
+      <c r="B4" s="63" cm="1">
+        <f t="array" ref="B4">(AVERAGE('Sheet 2 - Базовые переменные'!$B$3:$B$4))+$A4*'Sheet 2 - Базовые переменные'!$B$6*'Sheet 2 - Базовые переменные'!$B$7</f>
+        <v>8.5</v>
+      </c>
+      <c r="C4" s="64" cm="1">
+        <f t="array" ref="C4">'Sheet 2 - Синие карты'!$F$13*$A4</f>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D4" s="64" cm="1">
+        <f t="array" ref="D4">'Sheet 2 - Красные карты'!$F$13*$A4</f>
+        <v>-4.95</v>
+      </c>
+      <c r="E4" s="64" cm="1">
+        <f t="array" ref="E4">'Sheet 2 - Фиолетовые карты'!$F$4*$A4</f>
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="F4" s="64" cm="1">
+        <f t="array" ref="F4">'Sheet 2 - Золотые карты'!$F$6*$A4</f>
+        <v>4</v>
+      </c>
+      <c r="G4" s="64" cm="1">
+        <f t="array" ref="G4">SUM(B4:F4)</f>
+        <v>16.908</v>
+      </c>
+      <c r="H4" s="64" cm="1">
+        <f t="array" ref="H4">AVERAGE('Sheet 2 - Синие карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$3,'Sheet 2 - Красные карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$4,'Sheet 2 - Фиолетовые карты'!D$4*'Sheet 2 - Вероятность выпадения'!B$5,'Sheet 2 - Золотые карты'!D$6*'Sheet 2 - Вероятность выпадения'!B$6)</f>
+        <v>1.2505025</v>
+      </c>
+      <c r="I4" s="64" cm="1">
+        <f t="array" ref="I4">G4/'Sheet 2 - Базовые переменные'!$B$7-H4</f>
+        <v>2.9764975</v>
+      </c>
+    </row>
+    <row r="5" ht="20.05" customHeight="1">
+      <c r="A5" s="65">
+        <v>2</v>
+      </c>
+      <c r="B5" s="66" cm="1">
+        <f t="array" ref="B5">(AVERAGE('Sheet 2 - Базовые переменные'!$B$3:$B$4))+$A5*'Sheet 2 - Базовые переменные'!$B$6*'Sheet 2 - Базовые переменные'!$B$7</f>
+        <v>10.5</v>
+      </c>
+      <c r="C5" s="67" cm="1">
+        <f t="array" ref="C5">'Sheet 2 - Синие карты'!$F$13*$A5</f>
+        <v>17.6</v>
+      </c>
+      <c r="D5" s="67" cm="1">
+        <f t="array" ref="D5">'Sheet 2 - Красные карты'!$F$13*$A5</f>
+        <v>-9.9</v>
+      </c>
+      <c r="E5" s="67" cm="1">
+        <f t="array" ref="E5">'Sheet 2 - Фиолетовые карты'!$F$4*$A5</f>
+        <v>1.116</v>
+      </c>
+      <c r="F5" s="67" cm="1">
+        <f t="array" ref="F5">'Sheet 2 - Золотые карты'!$F$6*$A5</f>
+        <v>8</v>
+      </c>
+      <c r="G5" s="67" cm="1">
+        <f t="array" ref="G5">SUM(B5:F5)</f>
+        <v>27.316</v>
+      </c>
+      <c r="H5" s="67" cm="1">
+        <f t="array" ref="H5">AVERAGE('Sheet 2 - Синие карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$3,'Sheet 2 - Красные карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$4,'Sheet 2 - Фиолетовые карты'!D$4*'Sheet 2 - Вероятность выпадения'!B$5,'Sheet 2 - Золотые карты'!D$6*'Sheet 2 - Вероятность выпадения'!B$6)</f>
+        <v>1.2505025</v>
+      </c>
+      <c r="I5" s="67" cm="1">
+        <f t="array" ref="I5">G5/'Sheet 2 - Базовые переменные'!$B$7-H5</f>
+        <v>5.5784975</v>
+      </c>
+    </row>
+    <row r="6" ht="20.05" customHeight="1">
+      <c r="A6" s="65">
+        <v>3</v>
+      </c>
+      <c r="B6" s="66" cm="1">
+        <f t="array" ref="B6">(AVERAGE('Sheet 2 - Базовые переменные'!$B$3:$B$4))+$A6*'Sheet 2 - Базовые переменные'!$B$6*'Sheet 2 - Базовые переменные'!$B$7</f>
+        <v>12.5</v>
+      </c>
+      <c r="C6" s="67" cm="1">
+        <f t="array" ref="C6">'Sheet 2 - Синие карты'!$F$13*$A6</f>
+        <v>26.4</v>
+      </c>
+      <c r="D6" s="67" cm="1">
+        <f t="array" ref="D6">'Sheet 2 - Красные карты'!$F$13*$A6</f>
+        <v>-14.85</v>
+      </c>
+      <c r="E6" s="67" cm="1">
+        <f t="array" ref="E6">'Sheet 2 - Фиолетовые карты'!$F$4*$A6</f>
+        <v>1.674</v>
+      </c>
+      <c r="F6" s="67" cm="1">
+        <f t="array" ref="F6">'Sheet 2 - Золотые карты'!$F$6*$A6</f>
+        <v>12</v>
+      </c>
+      <c r="G6" s="67" cm="1">
+        <f t="array" ref="G6">SUM(B6:F6)</f>
+        <v>37.724</v>
+      </c>
+      <c r="H6" s="67" cm="1">
+        <f t="array" ref="H6">AVERAGE('Sheet 2 - Синие карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$3,'Sheet 2 - Красные карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$4,'Sheet 2 - Фиолетовые карты'!D$4*'Sheet 2 - Вероятность выпадения'!B$5,'Sheet 2 - Золотые карты'!D$6*'Sheet 2 - Вероятность выпадения'!B$6)</f>
+        <v>1.2505025</v>
+      </c>
+      <c r="I6" s="67" cm="1">
+        <f t="array" ref="I6">G6/'Sheet 2 - Базовые переменные'!$B$7-H6</f>
+        <v>8.1804975</v>
+      </c>
+    </row>
+    <row r="7" ht="20.05" customHeight="1">
+      <c r="A7" s="65">
+        <v>4</v>
+      </c>
+      <c r="B7" s="66" cm="1">
+        <f t="array" ref="B7">(AVERAGE('Sheet 2 - Базовые переменные'!$B$3:$B$4))+$A7*'Sheet 2 - Базовые переменные'!$B$6*'Sheet 2 - Базовые переменные'!$B$7</f>
+        <v>14.5</v>
+      </c>
+      <c r="C7" s="67" cm="1">
+        <f t="array" ref="C7">'Sheet 2 - Синие карты'!$F$13*$A7</f>
+        <v>35.2</v>
+      </c>
+      <c r="D7" s="67" cm="1">
+        <f t="array" ref="D7">'Sheet 2 - Красные карты'!$F$13*$A7</f>
+        <v>-19.8</v>
+      </c>
+      <c r="E7" s="67" cm="1">
+        <f t="array" ref="E7">'Sheet 2 - Фиолетовые карты'!$F$4*$A7</f>
+        <v>2.232</v>
+      </c>
+      <c r="F7" s="67" cm="1">
+        <f t="array" ref="F7">'Sheet 2 - Золотые карты'!$F$6*$A7</f>
+        <v>16</v>
+      </c>
+      <c r="G7" s="67" cm="1">
+        <f t="array" ref="G7">SUM(B7:F7)</f>
+        <v>48.132</v>
+      </c>
+      <c r="H7" s="67" cm="1">
+        <f t="array" ref="H7">AVERAGE('Sheet 2 - Синие карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$3,'Sheet 2 - Красные карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$4,'Sheet 2 - Фиолетовые карты'!D$4*'Sheet 2 - Вероятность выпадения'!B$5,'Sheet 2 - Золотые карты'!D$6*'Sheet 2 - Вероятность выпадения'!B$6)</f>
+        <v>1.2505025</v>
+      </c>
+      <c r="I7" s="67" cm="1">
+        <f t="array" ref="I7">G7/'Sheet 2 - Базовые переменные'!$B$7-H7</f>
+        <v>10.7824975</v>
+      </c>
+    </row>
+    <row r="8" ht="20.05" customHeight="1">
+      <c r="A8" s="65">
+        <v>5</v>
+      </c>
+      <c r="B8" s="66" cm="1">
+        <f t="array" ref="B8">(AVERAGE('Sheet 2 - Базовые переменные'!$B$3:$B$4))+$A8*'Sheet 2 - Базовые переменные'!$B$6*'Sheet 2 - Базовые переменные'!$B$7</f>
+        <v>16.5</v>
+      </c>
+      <c r="C8" s="67" cm="1">
+        <f t="array" ref="C8">'Sheet 2 - Синие карты'!$F$13*$A8</f>
+        <v>44</v>
+      </c>
+      <c r="D8" s="67" cm="1">
+        <f t="array" ref="D8">'Sheet 2 - Красные карты'!$F$13*$A8</f>
+        <v>-24.75</v>
+      </c>
+      <c r="E8" s="67" cm="1">
+        <f t="array" ref="E8">'Sheet 2 - Фиолетовые карты'!$F$4*$A8</f>
+        <v>2.79</v>
+      </c>
+      <c r="F8" s="67" cm="1">
+        <f t="array" ref="F8">'Sheet 2 - Золотые карты'!$F$6*$A8</f>
+        <v>20</v>
+      </c>
+      <c r="G8" s="67" cm="1">
+        <f t="array" ref="G8">SUM(B8:F8)</f>
+        <v>58.54</v>
+      </c>
+      <c r="H8" s="67" cm="1">
+        <f t="array" ref="H8">AVERAGE('Sheet 2 - Синие карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$3,'Sheet 2 - Красные карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$4,'Sheet 2 - Фиолетовые карты'!D$4*'Sheet 2 - Вероятность выпадения'!B$5,'Sheet 2 - Золотые карты'!D$6*'Sheet 2 - Вероятность выпадения'!B$6)</f>
+        <v>1.2505025</v>
+      </c>
+      <c r="I8" s="67" cm="1">
+        <f t="array" ref="I8">G8/'Sheet 2 - Базовые переменные'!$B$7-H8</f>
+        <v>13.3844975</v>
+      </c>
+    </row>
+    <row r="9" ht="20.05" customHeight="1">
+      <c r="A9" s="65">
+        <v>6</v>
+      </c>
+      <c r="B9" s="66" cm="1">
+        <f t="array" ref="B9">(AVERAGE('Sheet 2 - Базовые переменные'!$B$3:$B$4))+$A9*'Sheet 2 - Базовые переменные'!$B$6*'Sheet 2 - Базовые переменные'!$B$7</f>
+        <v>18.5</v>
+      </c>
+      <c r="C9" s="67" cm="1">
+        <f t="array" ref="C9">'Sheet 2 - Синие карты'!$F$13*$A9</f>
+        <v>52.8</v>
+      </c>
+      <c r="D9" s="67" cm="1">
+        <f t="array" ref="D9">'Sheet 2 - Красные карты'!$F$13*$A9</f>
+        <v>-29.7</v>
+      </c>
+      <c r="E9" s="67" cm="1">
+        <f t="array" ref="E9">'Sheet 2 - Фиолетовые карты'!$F$4*$A9</f>
+        <v>3.348</v>
+      </c>
+      <c r="F9" s="67" cm="1">
+        <f t="array" ref="F9">'Sheet 2 - Золотые карты'!$F$6*$A9</f>
+        <v>24</v>
+      </c>
+      <c r="G9" s="67" cm="1">
+        <f t="array" ref="G9">SUM(B9:F9)</f>
+        <v>68.94799999999999</v>
+      </c>
+      <c r="H9" s="67" cm="1">
+        <f t="array" ref="H9">AVERAGE('Sheet 2 - Синие карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$3,'Sheet 2 - Красные карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$4,'Sheet 2 - Фиолетовые карты'!D$4*'Sheet 2 - Вероятность выпадения'!B$5,'Sheet 2 - Золотые карты'!D$6*'Sheet 2 - Вероятность выпадения'!B$6)</f>
+        <v>1.2505025</v>
+      </c>
+      <c r="I9" s="67" cm="1">
+        <f t="array" ref="I9">G9/'Sheet 2 - Базовые переменные'!$B$7-H9</f>
+        <v>15.9864975</v>
+      </c>
+    </row>
+    <row r="10" ht="20.05" customHeight="1">
+      <c r="A10" s="65">
+        <v>7</v>
+      </c>
+      <c r="B10" s="66" cm="1">
+        <f t="array" ref="B10">(AVERAGE('Sheet 2 - Базовые переменные'!$B$3:$B$4))+$A10*'Sheet 2 - Базовые переменные'!$B$6*'Sheet 2 - Базовые переменные'!$B$7</f>
+        <v>20.5</v>
+      </c>
+      <c r="C10" s="67" cm="1">
+        <f t="array" ref="C10">'Sheet 2 - Синие карты'!$F$13*$A10</f>
+        <v>61.6</v>
+      </c>
+      <c r="D10" s="67" cm="1">
+        <f t="array" ref="D10">'Sheet 2 - Красные карты'!$F$13*$A10</f>
+        <v>-34.65</v>
+      </c>
+      <c r="E10" s="67" cm="1">
+        <f t="array" ref="E10">'Sheet 2 - Фиолетовые карты'!$F$4*$A10</f>
+        <v>3.906</v>
+      </c>
+      <c r="F10" s="67" cm="1">
+        <f t="array" ref="F10">'Sheet 2 - Золотые карты'!$F$6*$A10</f>
+        <v>28</v>
+      </c>
+      <c r="G10" s="67" cm="1">
+        <f t="array" ref="G10">SUM(B10:F10)</f>
+        <v>79.35599999999999</v>
+      </c>
+      <c r="H10" s="67" cm="1">
+        <f t="array" ref="H10">AVERAGE('Sheet 2 - Синие карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$3,'Sheet 2 - Красные карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$4,'Sheet 2 - Фиолетовые карты'!D$4*'Sheet 2 - Вероятность выпадения'!B$5,'Sheet 2 - Золотые карты'!D$6*'Sheet 2 - Вероятность выпадения'!B$6)</f>
+        <v>1.2505025</v>
+      </c>
+      <c r="I10" s="67" cm="1">
+        <f t="array" ref="I10">G10/'Sheet 2 - Базовые переменные'!$B$7-H10</f>
+        <v>18.5884975</v>
+      </c>
+    </row>
+    <row r="11" ht="20.05" customHeight="1">
+      <c r="A11" s="65">
+        <v>8</v>
+      </c>
+      <c r="B11" s="66" cm="1">
+        <f t="array" ref="B11">(AVERAGE('Sheet 2 - Базовые переменные'!$B$3:$B$4))+$A11*'Sheet 2 - Базовые переменные'!$B$6*'Sheet 2 - Базовые переменные'!$B$7</f>
+        <v>22.5</v>
+      </c>
+      <c r="C11" s="67" cm="1">
+        <f t="array" ref="C11">'Sheet 2 - Синие карты'!$F$13*$A11</f>
+        <v>70.40000000000001</v>
+      </c>
+      <c r="D11" s="67" cm="1">
+        <f t="array" ref="D11">'Sheet 2 - Красные карты'!$F$13*$A11</f>
+        <v>-39.6</v>
+      </c>
+      <c r="E11" s="67" cm="1">
+        <f t="array" ref="E11">'Sheet 2 - Фиолетовые карты'!$F$4*$A11</f>
+        <v>4.464</v>
+      </c>
+      <c r="F11" s="67" cm="1">
+        <f t="array" ref="F11">'Sheet 2 - Золотые карты'!$F$6*$A11</f>
+        <v>32</v>
+      </c>
+      <c r="G11" s="67" cm="1">
+        <f t="array" ref="G11">SUM(B11:F11)</f>
+        <v>89.764</v>
+      </c>
+      <c r="H11" s="67" cm="1">
+        <f t="array" ref="H11">AVERAGE('Sheet 2 - Синие карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$3,'Sheet 2 - Красные карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$4,'Sheet 2 - Фиолетовые карты'!D$4*'Sheet 2 - Вероятность выпадения'!B$5,'Sheet 2 - Золотые карты'!D$6*'Sheet 2 - Вероятность выпадения'!B$6)</f>
+        <v>1.2505025</v>
+      </c>
+      <c r="I11" s="67" cm="1">
+        <f t="array" ref="I11">G11/'Sheet 2 - Базовые переменные'!$B$7-H11</f>
+        <v>21.1904975</v>
+      </c>
+    </row>
+    <row r="12" ht="20.05" customHeight="1">
+      <c r="A12" s="65">
+        <v>9</v>
+      </c>
+      <c r="B12" s="66" cm="1">
+        <f t="array" ref="B12">(AVERAGE('Sheet 2 - Базовые переменные'!$B$3:$B$4))+$A12*'Sheet 2 - Базовые переменные'!$B$6*'Sheet 2 - Базовые переменные'!$B$7</f>
+        <v>24.5</v>
+      </c>
+      <c r="C12" s="67" cm="1">
+        <f t="array" ref="C12">'Sheet 2 - Синие карты'!$F$13*$A12</f>
+        <v>79.2</v>
+      </c>
+      <c r="D12" s="67" cm="1">
+        <f t="array" ref="D12">'Sheet 2 - Красные карты'!$F$13*$A12</f>
+        <v>-44.55</v>
+      </c>
+      <c r="E12" s="67" cm="1">
+        <f t="array" ref="E12">'Sheet 2 - Фиолетовые карты'!$F$4*$A12</f>
+        <v>5.022</v>
+      </c>
+      <c r="F12" s="67" cm="1">
+        <f t="array" ref="F12">'Sheet 2 - Золотые карты'!$F$6*$A12</f>
+        <v>36</v>
+      </c>
+      <c r="G12" s="67" cm="1">
+        <f t="array" ref="G12">SUM(B12:F12)</f>
+        <v>100.172</v>
+      </c>
+      <c r="H12" s="67" cm="1">
+        <f t="array" ref="H12">AVERAGE('Sheet 2 - Синие карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$3,'Sheet 2 - Красные карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$4,'Sheet 2 - Фиолетовые карты'!D$4*'Sheet 2 - Вероятность выпадения'!B$5,'Sheet 2 - Золотые карты'!D$6*'Sheet 2 - Вероятность выпадения'!B$6)</f>
+        <v>1.2505025</v>
+      </c>
+      <c r="I12" s="67" cm="1">
+        <f t="array" ref="I12">G12/'Sheet 2 - Базовые переменные'!$B$7-H12</f>
+        <v>23.7924975</v>
+      </c>
+    </row>
+    <row r="13" ht="20.05" customHeight="1">
+      <c r="A13" s="65">
+        <v>10</v>
+      </c>
+      <c r="B13" s="66" cm="1">
+        <f t="array" ref="B13">(AVERAGE('Sheet 2 - Базовые переменные'!$B$3:$B$4))+$A13*'Sheet 2 - Базовые переменные'!$B$6*'Sheet 2 - Базовые переменные'!$B$7</f>
+        <v>26.5</v>
+      </c>
+      <c r="C13" s="67" cm="1">
+        <f t="array" ref="C13">'Sheet 2 - Синие карты'!$F$13*$A13</f>
+        <v>88</v>
+      </c>
+      <c r="D13" s="67" cm="1">
+        <f t="array" ref="D13">'Sheet 2 - Красные карты'!$F$13*$A13</f>
+        <v>-49.5</v>
+      </c>
+      <c r="E13" s="67" cm="1">
+        <f t="array" ref="E13">'Sheet 2 - Фиолетовые карты'!$F$4*$A13</f>
+        <v>5.58</v>
+      </c>
+      <c r="F13" s="67" cm="1">
+        <f t="array" ref="F13">'Sheet 2 - Золотые карты'!$F$6*$A13</f>
+        <v>40</v>
+      </c>
+      <c r="G13" s="67" cm="1">
+        <f t="array" ref="G13">SUM(B13:F13)</f>
+        <v>110.58</v>
+      </c>
+      <c r="H13" s="67" cm="1">
+        <f t="array" ref="H13">AVERAGE('Sheet 2 - Синие карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$3,'Sheet 2 - Красные карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$4,'Sheet 2 - Фиолетовые карты'!D$4*'Sheet 2 - Вероятность выпадения'!B$5,'Sheet 2 - Золотые карты'!D$6*'Sheet 2 - Вероятность выпадения'!B$6)</f>
+        <v>1.2505025</v>
+      </c>
+      <c r="I13" s="67" cm="1">
+        <f t="array" ref="I13">G13/'Sheet 2 - Базовые переменные'!$B$7-H13</f>
+        <v>26.3944975</v>
+      </c>
+    </row>
+    <row r="14" ht="20.05" customHeight="1">
+      <c r="A14" s="65">
+        <v>11</v>
+      </c>
+      <c r="B14" s="66" cm="1">
+        <f t="array" ref="B14">(AVERAGE('Sheet 2 - Базовые переменные'!$B$3:$B$4))+$A14*'Sheet 2 - Базовые переменные'!$B$6*'Sheet 2 - Базовые переменные'!$B$7</f>
+        <v>28.5</v>
+      </c>
+      <c r="C14" s="67" cm="1">
+        <f t="array" ref="C14">'Sheet 2 - Синие карты'!$F$13*$A14</f>
+        <v>96.8</v>
+      </c>
+      <c r="D14" s="67" cm="1">
+        <f t="array" ref="D14">'Sheet 2 - Красные карты'!$F$13*$A14</f>
+        <v>-54.45</v>
+      </c>
+      <c r="E14" s="67" cm="1">
+        <f t="array" ref="E14">'Sheet 2 - Фиолетовые карты'!$F$4*$A14</f>
+        <v>6.138</v>
+      </c>
+      <c r="F14" s="67" cm="1">
+        <f t="array" ref="F14">'Sheet 2 - Золотые карты'!$F$6*$A14</f>
+        <v>44</v>
+      </c>
+      <c r="G14" s="67" cm="1">
+        <f t="array" ref="G14">SUM(B14:F14)</f>
+        <v>120.988</v>
+      </c>
+      <c r="H14" s="67" cm="1">
+        <f t="array" ref="H14">AVERAGE('Sheet 2 - Синие карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$3,'Sheet 2 - Красные карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$4,'Sheet 2 - Фиолетовые карты'!D$4*'Sheet 2 - Вероятность выпадения'!B$5,'Sheet 2 - Золотые карты'!D$6*'Sheet 2 - Вероятность выпадения'!B$6)</f>
+        <v>1.2505025</v>
+      </c>
+      <c r="I14" s="67" cm="1">
+        <f t="array" ref="I14">G14/'Sheet 2 - Базовые переменные'!$B$7-H14</f>
+        <v>28.9964975</v>
+      </c>
+    </row>
+    <row r="15" ht="20.05" customHeight="1">
+      <c r="A15" s="65">
+        <v>12</v>
+      </c>
+      <c r="B15" s="66" cm="1">
+        <f t="array" ref="B15">(AVERAGE('Sheet 2 - Базовые переменные'!$B$3:$B$4))+$A15*'Sheet 2 - Базовые переменные'!$B$6*'Sheet 2 - Базовые переменные'!$B$7</f>
+        <v>30.5</v>
+      </c>
+      <c r="C15" s="67" cm="1">
+        <f t="array" ref="C15">'Sheet 2 - Синие карты'!$F$13*$A15</f>
+        <v>105.6</v>
+      </c>
+      <c r="D15" s="67" cm="1">
+        <f t="array" ref="D15">'Sheet 2 - Красные карты'!$F$13*$A15</f>
+        <v>-59.4</v>
+      </c>
+      <c r="E15" s="67" cm="1">
+        <f t="array" ref="E15">'Sheet 2 - Фиолетовые карты'!$F$4*$A15</f>
+        <v>6.696</v>
+      </c>
+      <c r="F15" s="67" cm="1">
+        <f t="array" ref="F15">'Sheet 2 - Золотые карты'!$F$6*$A15</f>
+        <v>48</v>
+      </c>
+      <c r="G15" s="67" cm="1">
+        <f t="array" ref="G15">SUM(B15:F15)</f>
+        <v>131.396</v>
+      </c>
+      <c r="H15" s="67" cm="1">
+        <f t="array" ref="H15">AVERAGE('Sheet 2 - Синие карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$3,'Sheet 2 - Красные карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$4,'Sheet 2 - Фиолетовые карты'!D$4*'Sheet 2 - Вероятность выпадения'!B$5,'Sheet 2 - Золотые карты'!D$6*'Sheet 2 - Вероятность выпадения'!B$6)</f>
+        <v>1.2505025</v>
+      </c>
+      <c r="I15" s="67" cm="1">
+        <f t="array" ref="I15">G15/'Sheet 2 - Базовые переменные'!$B$7-H15</f>
+        <v>31.5984975</v>
+      </c>
+    </row>
+    <row r="16" ht="20.05" customHeight="1">
+      <c r="A16" s="65">
+        <v>13</v>
+      </c>
+      <c r="B16" s="66" cm="1">
+        <f t="array" ref="B16">(AVERAGE('Sheet 2 - Базовые переменные'!$B$3:$B$4))+$A16*'Sheet 2 - Базовые переменные'!$B$6*'Sheet 2 - Базовые переменные'!$B$7</f>
+        <v>32.5</v>
+      </c>
+      <c r="C16" s="67" cm="1">
+        <f t="array" ref="C16">'Sheet 2 - Синие карты'!$F$13*$A16</f>
+        <v>114.4</v>
+      </c>
+      <c r="D16" s="67" cm="1">
+        <f t="array" ref="D16">'Sheet 2 - Красные карты'!$F$13*$A16</f>
+        <v>-64.34999999999999</v>
+      </c>
+      <c r="E16" s="67" cm="1">
+        <f t="array" ref="E16">'Sheet 2 - Фиолетовые карты'!$F$4*$A16</f>
+        <v>7.254</v>
+      </c>
+      <c r="F16" s="67" cm="1">
+        <f t="array" ref="F16">'Sheet 2 - Золотые карты'!$F$6*$A16</f>
+        <v>52</v>
+      </c>
+      <c r="G16" s="67" cm="1">
+        <f t="array" ref="G16">SUM(B16:F16)</f>
+        <v>141.804</v>
+      </c>
+      <c r="H16" s="67" cm="1">
+        <f t="array" ref="H16">AVERAGE('Sheet 2 - Синие карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$3,'Sheet 2 - Красные карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$4,'Sheet 2 - Фиолетовые карты'!D$4*'Sheet 2 - Вероятность выпадения'!B$5,'Sheet 2 - Золотые карты'!D$6*'Sheet 2 - Вероятность выпадения'!B$6)</f>
+        <v>1.2505025</v>
+      </c>
+      <c r="I16" s="67" cm="1">
+        <f t="array" ref="I16">G16/'Sheet 2 - Базовые переменные'!$B$7-H16</f>
+        <v>34.2004975</v>
+      </c>
+    </row>
+    <row r="17" ht="20.05" customHeight="1">
+      <c r="A17" s="65">
+        <v>14</v>
+      </c>
+      <c r="B17" s="66" cm="1">
+        <f t="array" ref="B17">(AVERAGE('Sheet 2 - Базовые переменные'!$B$3:$B$4))+$A17*'Sheet 2 - Базовые переменные'!$B$6*'Sheet 2 - Базовые переменные'!$B$7</f>
+        <v>34.5</v>
+      </c>
+      <c r="C17" s="67" cm="1">
+        <f t="array" ref="C17">'Sheet 2 - Синие карты'!$F$13*$A17</f>
+        <v>123.2</v>
+      </c>
+      <c r="D17" s="67" cm="1">
+        <f t="array" ref="D17">'Sheet 2 - Красные карты'!$F$13*$A17</f>
+        <v>-69.3</v>
+      </c>
+      <c r="E17" s="67" cm="1">
+        <f t="array" ref="E17">'Sheet 2 - Фиолетовые карты'!$F$4*$A17</f>
+        <v>7.812</v>
+      </c>
+      <c r="F17" s="67" cm="1">
+        <f t="array" ref="F17">'Sheet 2 - Золотые карты'!$F$6*$A17</f>
+        <v>56</v>
+      </c>
+      <c r="G17" s="67" cm="1">
+        <f t="array" ref="G17">SUM(B17:F17)</f>
+        <v>152.212</v>
+      </c>
+      <c r="H17" s="67" cm="1">
+        <f t="array" ref="H17">AVERAGE('Sheet 2 - Синие карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$3,'Sheet 2 - Красные карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$4,'Sheet 2 - Фиолетовые карты'!D$4*'Sheet 2 - Вероятность выпадения'!B$5,'Sheet 2 - Золотые карты'!D$6*'Sheet 2 - Вероятность выпадения'!B$6)</f>
+        <v>1.2505025</v>
+      </c>
+      <c r="I17" s="67" cm="1">
+        <f t="array" ref="I17">G17/'Sheet 2 - Базовые переменные'!$B$7-H17</f>
+        <v>36.8024975</v>
+      </c>
+    </row>
+    <row r="18" ht="20.05" customHeight="1">
+      <c r="A18" s="65">
+        <v>15</v>
+      </c>
+      <c r="B18" s="66" cm="1">
+        <f t="array" ref="B18">(AVERAGE('Sheet 2 - Базовые переменные'!$B$3:$B$4))+$A18*'Sheet 2 - Базовые переменные'!$B$6*'Sheet 2 - Базовые переменные'!$B$7</f>
+        <v>36.5</v>
+      </c>
+      <c r="C18" s="67" cm="1">
+        <f t="array" ref="C18">'Sheet 2 - Синие карты'!$F$13*$A18</f>
+        <v>132</v>
+      </c>
+      <c r="D18" s="67" cm="1">
+        <f t="array" ref="D18">'Sheet 2 - Красные карты'!$F$13*$A18</f>
+        <v>-74.25</v>
+      </c>
+      <c r="E18" s="67" cm="1">
+        <f t="array" ref="E18">'Sheet 2 - Фиолетовые карты'!$F$4*$A18</f>
+        <v>8.369999999999999</v>
+      </c>
+      <c r="F18" s="67" cm="1">
+        <f t="array" ref="F18">'Sheet 2 - Золотые карты'!$F$6*$A18</f>
+        <v>60</v>
+      </c>
+      <c r="G18" s="67" cm="1">
+        <f t="array" ref="G18">SUM(B18:F18)</f>
+        <v>162.62</v>
+      </c>
+      <c r="H18" s="67" cm="1">
+        <f t="array" ref="H18">AVERAGE('Sheet 2 - Синие карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$3,'Sheet 2 - Красные карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$4,'Sheet 2 - Фиолетовые карты'!D$4*'Sheet 2 - Вероятность выпадения'!B$5,'Sheet 2 - Золотые карты'!D$6*'Sheet 2 - Вероятность выпадения'!B$6)</f>
+        <v>1.2505025</v>
+      </c>
+      <c r="I18" s="67" cm="1">
+        <f t="array" ref="I18">G18/'Sheet 2 - Базовые переменные'!$B$7-H18</f>
+        <v>39.4044975</v>
+      </c>
+    </row>
+    <row r="19" ht="20.05" customHeight="1">
+      <c r="A19" s="65">
+        <v>16</v>
+      </c>
+      <c r="B19" s="66" cm="1">
+        <f t="array" ref="B19">(AVERAGE('Sheet 2 - Базовые переменные'!$B$3:$B$4))+$A19*'Sheet 2 - Базовые переменные'!$B$6*'Sheet 2 - Базовые переменные'!$B$7</f>
+        <v>38.5</v>
+      </c>
+      <c r="C19" s="67" cm="1">
+        <f t="array" ref="C19">'Sheet 2 - Синие карты'!$F$13*$A19</f>
+        <v>140.8</v>
+      </c>
+      <c r="D19" s="67" cm="1">
+        <f t="array" ref="D19">'Sheet 2 - Красные карты'!$F$13*$A19</f>
+        <v>-79.2</v>
+      </c>
+      <c r="E19" s="67" cm="1">
+        <f t="array" ref="E19">'Sheet 2 - Фиолетовые карты'!$F$4*$A19</f>
+        <v>8.928000000000001</v>
+      </c>
+      <c r="F19" s="67" cm="1">
+        <f t="array" ref="F19">'Sheet 2 - Золотые карты'!$F$6*$A19</f>
+        <v>64</v>
+      </c>
+      <c r="G19" s="67" cm="1">
+        <f t="array" ref="G19">SUM(B19:F19)</f>
+        <v>173.028</v>
+      </c>
+      <c r="H19" s="67" cm="1">
+        <f t="array" ref="H19">AVERAGE('Sheet 2 - Синие карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$3,'Sheet 2 - Красные карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$4,'Sheet 2 - Фиолетовые карты'!D$4*'Sheet 2 - Вероятность выпадения'!B$5,'Sheet 2 - Золотые карты'!D$6*'Sheet 2 - Вероятность выпадения'!B$6)</f>
+        <v>1.2505025</v>
+      </c>
+      <c r="I19" s="67" cm="1">
+        <f t="array" ref="I19">G19/'Sheet 2 - Базовые переменные'!$B$7-H19</f>
+        <v>42.0064975</v>
+      </c>
+    </row>
+    <row r="20" ht="20.05" customHeight="1">
+      <c r="A20" s="65">
+        <v>17</v>
+      </c>
+      <c r="B20" s="66" cm="1">
+        <f t="array" ref="B20">(AVERAGE('Sheet 2 - Базовые переменные'!$B$3:$B$4))+$A20*'Sheet 2 - Базовые переменные'!$B$6*'Sheet 2 - Базовые переменные'!$B$7</f>
+        <v>40.5</v>
+      </c>
+      <c r="C20" s="67" cm="1">
+        <f t="array" ref="C20">'Sheet 2 - Синие карты'!$F$13*$A20</f>
+        <v>149.6</v>
+      </c>
+      <c r="D20" s="67" cm="1">
+        <f t="array" ref="D20">'Sheet 2 - Красные карты'!$F$13*$A20</f>
+        <v>-84.15000000000001</v>
+      </c>
+      <c r="E20" s="67" cm="1">
+        <f t="array" ref="E20">'Sheet 2 - Фиолетовые карты'!$F$4*$A20</f>
+        <v>9.486000000000001</v>
+      </c>
+      <c r="F20" s="67" cm="1">
+        <f t="array" ref="F20">'Sheet 2 - Золотые карты'!$F$6*$A20</f>
+        <v>68</v>
+      </c>
+      <c r="G20" s="67" cm="1">
+        <f t="array" ref="G20">SUM(B20:F20)</f>
+        <v>183.436</v>
+      </c>
+      <c r="H20" s="67" cm="1">
+        <f t="array" ref="H20">AVERAGE('Sheet 2 - Синие карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$3,'Sheet 2 - Красные карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$4,'Sheet 2 - Фиолетовые карты'!D$4*'Sheet 2 - Вероятность выпадения'!B$5,'Sheet 2 - Золотые карты'!D$6*'Sheet 2 - Вероятность выпадения'!B$6)</f>
+        <v>1.2505025</v>
+      </c>
+      <c r="I20" s="67" cm="1">
+        <f t="array" ref="I20">G20/'Sheet 2 - Базовые переменные'!$B$7-H20</f>
+        <v>44.6084975</v>
+      </c>
+    </row>
+    <row r="21" ht="20.05" customHeight="1">
+      <c r="A21" s="65">
+        <v>18</v>
+      </c>
+      <c r="B21" s="66" cm="1">
+        <f t="array" ref="B21">(AVERAGE('Sheet 2 - Базовые переменные'!$B$3:$B$4))+$A21*'Sheet 2 - Базовые переменные'!$B$6*'Sheet 2 - Базовые переменные'!$B$7</f>
+        <v>42.5</v>
+      </c>
+      <c r="C21" s="67" cm="1">
+        <f t="array" ref="C21">'Sheet 2 - Синие карты'!$F$13*$A21</f>
+        <v>158.4</v>
+      </c>
+      <c r="D21" s="67" cm="1">
+        <f t="array" ref="D21">'Sheet 2 - Красные карты'!$F$13*$A21</f>
+        <v>-89.09999999999999</v>
+      </c>
+      <c r="E21" s="67" cm="1">
+        <f t="array" ref="E21">'Sheet 2 - Фиолетовые карты'!$F$4*$A21</f>
+        <v>10.044</v>
+      </c>
+      <c r="F21" s="67" cm="1">
+        <f t="array" ref="F21">'Sheet 2 - Золотые карты'!$F$6*$A21</f>
+        <v>72</v>
+      </c>
+      <c r="G21" s="67" cm="1">
+        <f t="array" ref="G21">SUM(B21:F21)</f>
+        <v>193.844</v>
+      </c>
+      <c r="H21" s="67" cm="1">
+        <f t="array" ref="H21">AVERAGE('Sheet 2 - Синие карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$3,'Sheet 2 - Красные карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$4,'Sheet 2 - Фиолетовые карты'!D$4*'Sheet 2 - Вероятность выпадения'!B$5,'Sheet 2 - Золотые карты'!D$6*'Sheet 2 - Вероятность выпадения'!B$6)</f>
+        <v>1.2505025</v>
+      </c>
+      <c r="I21" s="67" cm="1">
+        <f t="array" ref="I21">G21/'Sheet 2 - Базовые переменные'!$B$7-H21</f>
+        <v>47.2104975</v>
+      </c>
+    </row>
+    <row r="22" ht="20.05" customHeight="1">
+      <c r="A22" s="65">
+        <v>19</v>
+      </c>
+      <c r="B22" s="66" cm="1">
+        <f t="array" ref="B22">(AVERAGE('Sheet 2 - Базовые переменные'!$B$3:$B$4))+$A22*'Sheet 2 - Базовые переменные'!$B$6*'Sheet 2 - Базовые переменные'!$B$7</f>
+        <v>44.5</v>
+      </c>
+      <c r="C22" s="67" cm="1">
+        <f t="array" ref="C22">'Sheet 2 - Синие карты'!$F$13*$A22</f>
+        <v>167.2</v>
+      </c>
+      <c r="D22" s="67" cm="1">
+        <f t="array" ref="D22">'Sheet 2 - Красные карты'!$F$13*$A22</f>
+        <v>-94.05</v>
+      </c>
+      <c r="E22" s="67" cm="1">
+        <f t="array" ref="E22">'Sheet 2 - Фиолетовые карты'!$F$4*$A22</f>
+        <v>10.602</v>
+      </c>
+      <c r="F22" s="67" cm="1">
+        <f t="array" ref="F22">'Sheet 2 - Золотые карты'!$F$6*$A22</f>
+        <v>76</v>
+      </c>
+      <c r="G22" s="67" cm="1">
+        <f t="array" ref="G22">SUM(B22:F22)</f>
+        <v>204.252</v>
+      </c>
+      <c r="H22" s="67" cm="1">
+        <f t="array" ref="H22">AVERAGE('Sheet 2 - Синие карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$3,'Sheet 2 - Красные карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$4,'Sheet 2 - Фиолетовые карты'!D$4*'Sheet 2 - Вероятность выпадения'!B$5,'Sheet 2 - Золотые карты'!D$6*'Sheet 2 - Вероятность выпадения'!B$6)</f>
+        <v>1.2505025</v>
+      </c>
+      <c r="I22" s="67" cm="1">
+        <f t="array" ref="I22">G22/'Sheet 2 - Базовые переменные'!$B$7-H22</f>
+        <v>49.8124975</v>
+      </c>
+    </row>
+    <row r="23" ht="20.05" customHeight="1">
+      <c r="A23" s="65">
+        <v>20</v>
+      </c>
+      <c r="B23" s="66" cm="1">
+        <f t="array" ref="B23">(AVERAGE('Sheet 2 - Базовые переменные'!$B$3:$B$4))+$A23*'Sheet 2 - Базовые переменные'!$B$6*'Sheet 2 - Базовые переменные'!$B$7</f>
+        <v>46.5</v>
+      </c>
+      <c r="C23" s="67" cm="1">
+        <f t="array" ref="C23">'Sheet 2 - Синие карты'!$F$13*$A23</f>
+        <v>176</v>
+      </c>
+      <c r="D23" s="67" cm="1">
+        <f t="array" ref="D23">'Sheet 2 - Красные карты'!$F$13*$A23</f>
+        <v>-99</v>
+      </c>
+      <c r="E23" s="67" cm="1">
+        <f t="array" ref="E23">'Sheet 2 - Фиолетовые карты'!$F$4*$A23</f>
+        <v>11.16</v>
+      </c>
+      <c r="F23" s="67" cm="1">
+        <f t="array" ref="F23">'Sheet 2 - Золотые карты'!$F$6*$A23</f>
+        <v>80</v>
+      </c>
+      <c r="G23" s="67" cm="1">
+        <f t="array" ref="G23">SUM(B23:F23)</f>
+        <v>214.66</v>
+      </c>
+      <c r="H23" s="67" cm="1">
+        <f t="array" ref="H23">AVERAGE('Sheet 2 - Синие карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$3,'Sheet 2 - Красные карты'!D$13*'Sheet 2 - Вероятность выпадения'!B$4,'Sheet 2 - Фиолетовые карты'!D$4*'Sheet 2 - Вероятность выпадения'!B$5,'Sheet 2 - Золотые карты'!D$6*'Sheet 2 - Вероятность выпадения'!B$6)</f>
+        <v>1.2505025</v>
+      </c>
+      <c r="I23" s="67" cm="1">
+        <f t="array" ref="I23">G23/'Sheet 2 - Базовые переменные'!$B$7-H23</f>
+        <v>52.4144975</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="C2:F2"/>
+  </mergeCells>
+  <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:G4"/>
+  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="5" width="16.3516" style="68" customWidth="1"/>
+    <col min="6" max="6" width="18.4141" style="68" customWidth="1"/>
+    <col min="7" max="7" width="16.3516" style="68" customWidth="1"/>
+    <col min="8" max="16384" width="16.3516" style="68" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27.65" customHeight="1">
+      <c r="A1" t="s" s="29">
+        <v>176</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+    </row>
+    <row r="2" ht="32.25" customHeight="1">
+      <c r="A2" t="s" s="36">
+        <v>149</v>
+      </c>
+      <c r="B2" t="s" s="36">
+        <v>115</v>
+      </c>
+      <c r="C2" t="s" s="36">
+        <v>150</v>
+      </c>
+      <c r="D2" t="s" s="36">
+        <v>151</v>
+      </c>
+      <c r="E2" t="s" s="36">
+        <v>152</v>
+      </c>
+      <c r="F2" t="s" s="36">
+        <v>153</v>
+      </c>
+      <c r="G2" s="69"/>
+    </row>
+    <row r="3" ht="20.25" customHeight="1">
+      <c r="A3" s="38">
+        <v>1</v>
+      </c>
+      <c r="B3" s="39"/>
+      <c r="C3" t="s" s="40">
+        <v>162</v>
+      </c>
+      <c r="D3" s="41" cm="1">
+        <f t="array" ref="D3">F3/'Sheet 2 - Базовые переменные'!$B$7*VLOOKUP(C3,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>0.18135</v>
+      </c>
+      <c r="E3" s="41" cm="1">
+        <f t="array" ref="E3">'Sheet 2 - Синие карты'!F13*'Sheet 2 - Вероятность выпадения'!B3+'Sheet 2 - Красные карты'!F13*'Sheet 2 - Вероятность выпадения'!B4+'Sheet 2 - Золотые карты'!F6*'Sheet 2 - Вероятность выпадения'!B6</f>
+        <v>1.395</v>
+      </c>
+      <c r="F3" s="41" cm="1">
+        <f t="array" ref="F3">AVERAGE('Sheet 2 - Базовые переменные'!$B$8:$B$9)*E3*'Sheet 2 - Базовые переменные'!$B$7*VLOOKUP(C3,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>7.254</v>
+      </c>
+      <c r="G3" s="41"/>
+    </row>
+    <row r="4" ht="32.05" customHeight="1">
+      <c r="A4" s="50"/>
+      <c r="B4" t="s" s="51">
+        <v>155</v>
+      </c>
+      <c r="C4" s="70"/>
+      <c r="D4" s="47" cm="1">
+        <f t="array" ref="D4">AVERAGE(D2:D3)</f>
+        <v>0.18135</v>
+      </c>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47" cm="1">
+        <f t="array" ref="F4">AVERAGE(F3:F3)/AVERAGE('Sheet 2 - Базовые переменные'!B8:B9)</f>
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="G4" s="47"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3">
+      <formula1>"Синий,Красный,Фиолетовый,Золотой"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:G6"/>
+  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="5" width="16.3516" style="71" customWidth="1"/>
+    <col min="6" max="6" width="18.4141" style="71" customWidth="1"/>
+    <col min="7" max="7" width="16.3516" style="71" customWidth="1"/>
+    <col min="8" max="16384" width="16.3516" style="71" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27.65" customHeight="1">
+      <c r="A1" t="s" s="29">
+        <v>178</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+    </row>
+    <row r="2" ht="32.25" customHeight="1">
+      <c r="A2" t="s" s="36">
+        <v>149</v>
+      </c>
+      <c r="B2" t="s" s="36">
+        <v>115</v>
+      </c>
+      <c r="C2" t="s" s="36">
+        <v>150</v>
+      </c>
+      <c r="D2" t="s" s="36">
+        <v>151</v>
+      </c>
+      <c r="E2" t="s" s="36">
+        <v>152</v>
+      </c>
+      <c r="F2" t="s" s="36">
+        <v>153</v>
+      </c>
+      <c r="G2" s="37"/>
+    </row>
+    <row r="3" ht="20.25" customHeight="1">
+      <c r="A3" s="38">
+        <v>1</v>
+      </c>
+      <c r="B3" s="39"/>
+      <c r="C3" t="s" s="40">
+        <v>163</v>
+      </c>
+      <c r="D3" s="41" cm="1">
+        <f t="array" ref="D3">F3/'Sheet 2 - Базовые переменные'!$B$7*VLOOKUP(C3,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>3.25</v>
+      </c>
+      <c r="E3" s="42">
+        <v>1</v>
+      </c>
+      <c r="F3" s="41" cm="1">
+        <f t="array" ref="F3">AVERAGE('Sheet 2 - Базовые переменные'!$B$8:$B$9)*E3*'Sheet 2 - Базовые переменные'!$B$7*VLOOKUP(C3,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>26</v>
+      </c>
+      <c r="G3" s="43"/>
+    </row>
+    <row r="4" ht="20.05" customHeight="1">
+      <c r="A4" s="44">
+        <v>2</v>
+      </c>
+      <c r="B4" s="45"/>
+      <c r="C4" t="s" s="46">
+        <v>163</v>
+      </c>
+      <c r="D4" s="47" cm="1">
+        <f t="array" ref="D4">F4/'Sheet 2 - Базовые переменные'!$B$7*VLOOKUP(C4,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>6.5</v>
+      </c>
+      <c r="E4" s="48">
+        <v>2</v>
+      </c>
+      <c r="F4" s="47" cm="1">
+        <f t="array" ref="F4">AVERAGE('Sheet 2 - Базовые переменные'!$B$8:$B$9)*E4*'Sheet 2 - Базовые переменные'!$B$7*VLOOKUP(C4,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>52</v>
+      </c>
+      <c r="G4" s="49"/>
+    </row>
+    <row r="5" ht="20.05" customHeight="1">
+      <c r="A5" s="44">
+        <v>3</v>
+      </c>
+      <c r="B5" s="45"/>
+      <c r="C5" t="s" s="46">
+        <v>163</v>
+      </c>
+      <c r="D5" s="47" cm="1">
+        <f t="array" ref="D5">F5/'Sheet 2 - Базовые переменные'!$B$7*VLOOKUP(C5,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>9.75</v>
+      </c>
+      <c r="E5" s="48">
+        <v>3</v>
+      </c>
+      <c r="F5" s="47" cm="1">
+        <f t="array" ref="F5">AVERAGE('Sheet 2 - Базовые переменные'!$B$8:$B$9)*E5*'Sheet 2 - Базовые переменные'!$B$7*VLOOKUP(C5,'Sheet 2 - Вероятность выпадения'!$A2:$B6,2,FALSE)</f>
+        <v>78</v>
+      </c>
+      <c r="G5" s="49"/>
+    </row>
+    <row r="6" ht="32.05" customHeight="1">
+      <c r="A6" s="50"/>
+      <c r="B6" t="s" s="51">
+        <v>155</v>
+      </c>
+      <c r="C6" s="46"/>
+      <c r="D6" s="47" cm="1">
+        <f t="array" ref="D6">AVERAGE(D3:D5)</f>
+        <v>6.5</v>
+      </c>
+      <c r="E6" s="49"/>
+      <c r="F6" s="47" cm="1">
+        <f t="array" ref="F6">AVERAGE(F3:F5)/AVERAGE('Sheet 2 - Базовые переменные'!B8:B9)</f>
+        <v>4</v>
+      </c>
+      <c r="G6" s="49"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C5">
+      <formula1>"Синий,Красный,Фиолетовый,Золотой"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/Cards.xlsx
+++ b/Cards.xlsx
@@ -2320,7 +2320,7 @@
         <v>108</v>
       </c>
       <c r="D22" s="18">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E22" s="18">
         <v>100</v>

--- a/Cards.xlsx
+++ b/Cards.xlsx
@@ -355,7 +355,7 @@
     <t>Gold</t>
   </si>
   <si>
-    <t>GET 1</t>
+    <t>GET 6</t>
   </si>
   <si>
     <t>Flux_golden-coin-with-game-controller-icon_-radiant-light_-cartoo.png</t>
@@ -364,13 +364,13 @@
     <t>Ваш проект заметили! Первая выплата.</t>
   </si>
   <si>
-    <t>Получите 1 корм из банка</t>
+    <t>Получите 10 корма из банка</t>
   </si>
   <si>
     <t>Грант на балансировку</t>
   </si>
   <si>
-    <t>GET 2</t>
+    <t>GET 18</t>
   </si>
   <si>
     <t>Flux_grant-document-with-golden-seal_-iskander-signing_-cartoon-s.png</t>
@@ -379,13 +379,13 @@
     <t>Специальный грант на улучшение баланса.</t>
   </si>
   <si>
-    <t>Получите 2 корма из банка</t>
+    <t>Получите 20 корма из банка</t>
   </si>
   <si>
     <t>Инвестиции от Искандера</t>
   </si>
   <si>
-    <t>GET 3</t>
+    <t>GET 30</t>
   </si>
   <si>
     <t>Flux_iskander-as-angel-investor-with-golden-briefcase_-sparkles_-.png</t>
@@ -394,7 +394,7 @@
     <t>Искандер верит в ваш проект! Крупные инвестиции.</t>
   </si>
   <si>
-    <t>Получите 3 корма из банка</t>
+    <t>Получите 30 корма из банка</t>
   </si>
 </sst>
 </file>
@@ -1781,7 +1781,7 @@
         <v>18</v>
       </c>
       <c r="H3" s="10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I3" t="s" s="9">
         <v>14</v>
@@ -1810,7 +1810,7 @@
         <v>22</v>
       </c>
       <c r="H4" s="10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I4" t="s" s="9">
         <v>23</v>
@@ -1839,7 +1839,7 @@
         <v>27</v>
       </c>
       <c r="H5" s="10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I5" t="s" s="9">
         <v>23</v>
@@ -2030,10 +2030,10 @@
         <v>57</v>
       </c>
       <c r="D12" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F12" t="s" s="13">
         <v>58</v>
@@ -2059,10 +2059,10 @@
         <v>62</v>
       </c>
       <c r="D13" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" s="14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s" s="13">
         <v>63</v>
@@ -2088,10 +2088,10 @@
         <v>67</v>
       </c>
       <c r="D14" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E14" s="14">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F14" t="s" s="13">
         <v>68</v>
@@ -2117,10 +2117,10 @@
         <v>72</v>
       </c>
       <c r="D15" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E15" s="14">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F15" t="s" s="13">
         <v>73</v>
@@ -2146,10 +2146,10 @@
         <v>77</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E16" s="14">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F16" t="s" s="13">
         <v>78</v>
@@ -2175,10 +2175,10 @@
         <v>82</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E17" s="14">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F17" t="s" s="13">
         <v>83</v>
@@ -2204,10 +2204,10 @@
         <v>87</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E18" s="14">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="F18" t="s" s="13">
         <v>88</v>
@@ -2233,10 +2233,10 @@
         <v>92</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E19" s="14">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F19" t="s" s="13">
         <v>93</v>
@@ -2262,10 +2262,10 @@
         <v>97</v>
       </c>
       <c r="D20" s="14">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E20" s="14">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="F20" t="s" s="13">
         <v>98</v>
@@ -2291,10 +2291,10 @@
         <v>102</v>
       </c>
       <c r="D21" s="14">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E21" s="14">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F21" t="s" s="13">
         <v>103</v>
@@ -2320,10 +2320,10 @@
         <v>108</v>
       </c>
       <c r="D22" s="18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E22" s="18">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F22" t="s" s="17">
         <v>109</v>
@@ -2332,7 +2332,7 @@
         <v>110</v>
       </c>
       <c r="H22" s="18">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I22" t="s" s="17">
         <v>111</v>
@@ -2349,10 +2349,10 @@
         <v>114</v>
       </c>
       <c r="D23" s="22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" s="22">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F23" t="s" s="21">
         <v>115</v>
@@ -2378,10 +2378,10 @@
         <v>119</v>
       </c>
       <c r="D24" s="22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E24" s="22">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="F24" t="s" s="21">
         <v>120</v>
@@ -2410,7 +2410,7 @@
         <v>10</v>
       </c>
       <c r="E25" s="22">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F25" t="s" s="21">
         <v>125</v>

--- a/Cards.xlsx
+++ b/Cards.xlsx
@@ -70,6 +70,24 @@
     <t>Константин выложил гайд в чат — команда сыта и мотивирована.</t>
   </si>
   <si>
+    <t>Стипендия за проект</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>GET 6</t>
+  </si>
+  <si>
+    <t>Flux_golden-coin-with-game-controller-icon_-radiant-light_-cartoo.png</t>
+  </si>
+  <si>
+    <t>Ваш проект заметили! Первая выплата.</t>
+  </si>
+  <si>
+    <t>Получите 10 корма из банка</t>
+  </si>
+  <si>
     <t>Баланс-пати от Константина</t>
   </si>
   <si>
@@ -97,6 +115,24 @@
     <t>Спринт синхронизирован, команда в ресурсе.</t>
   </si>
   <si>
+    <t>Аудит кормов от Искандера</t>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>STEAL_MONEY ALL 1</t>
+  </si>
+  <si>
+    <t>Flux_cartoon-iskander-with-magnifying-glass-inspecting-ledger_-dr.png</t>
+  </si>
+  <si>
+    <t>Искандер проверяет бюджет. Найдены излишки — изымаются.</t>
+  </si>
+  <si>
+    <t>Заберите 1 корм у всех оппонентов</t>
+  </si>
+  <si>
     <t>Грант на корм для команды</t>
   </si>
   <si>
@@ -124,6 +160,21 @@
     <t>Искандер объясняет, как корм влияет на метрики.</t>
   </si>
   <si>
+    <t>Проверка ТЗ: штраф за ошибки</t>
+  </si>
+  <si>
+    <t>STEAL_MONEY ALL 2</t>
+  </si>
+  <si>
+    <t>Flux_konstantin-with-red-pen-marking-documents_-shadows_-humorous.png</t>
+  </si>
+  <si>
+    <t>Константин нашёл несоответствия в ТЗ. Штрафуем.</t>
+  </si>
+  <si>
+    <t>Заберите 2 корма у всех оппонентов</t>
+  </si>
+  <si>
     <t>Дедлайн продлён!</t>
   </si>
   <si>
@@ -178,37 +229,19 @@
     <t>Релиз состоялся! Все получают награду.</t>
   </si>
   <si>
-    <t>Аудит кормов от Искандера</t>
-  </si>
-  <si>
-    <t>Red</t>
-  </si>
-  <si>
-    <t>STEAL_MONEY ALL 1</t>
-  </si>
-  <si>
-    <t>Flux_cartoon-iskander-with-magnifying-glass-inspecting-ledger_-dr.png</t>
-  </si>
-  <si>
-    <t>Искандер проверяет бюджет. Найдены излишки — изымаются.</t>
-  </si>
-  <si>
-    <t>Заберите 1 корм у всех оппонентов</t>
-  </si>
-  <si>
-    <t>Проверка ТЗ: штраф за ошибки</t>
-  </si>
-  <si>
-    <t>STEAL_MONEY ALL 2</t>
-  </si>
-  <si>
-    <t>Flux_konstantin-with-red-pen-marking-documents_-shadows_-humorous.png</t>
-  </si>
-  <si>
-    <t>Константин нашёл несоответствия в ТЗ. Штрафуем.</t>
-  </si>
-  <si>
-    <t>Заберите 2 корма у всех оппонентов</t>
+    <t>Грант на балансировку</t>
+  </si>
+  <si>
+    <t>GET 18</t>
+  </si>
+  <si>
+    <t>Flux_grant-document-with-golden-seal_-iskander-signing_-cartoon-s.png</t>
+  </si>
+  <si>
+    <t>Специальный грант на улучшение баланса.</t>
+  </si>
+  <si>
+    <t>Получите 20 корма из банка</t>
   </si>
   <si>
     <t>Ревизия спринта</t>
@@ -241,6 +274,24 @@
     <t>Заберите 4 корма у всех оппонентов</t>
   </si>
   <si>
+    <t>Плагиат на митапе</t>
+  </si>
+  <si>
+    <t>Purple</t>
+  </si>
+  <si>
+    <t>STEAL_CARD RANDOM</t>
+  </si>
+  <si>
+    <t>Flux_mysterious-silhouette-sneaking-a-card-from-table_-purple-neo.png</t>
+  </si>
+  <si>
+    <t>Пока все обсуждали архитектуру, вы тихонько взяли чужую идею...</t>
+  </si>
+  <si>
+    <t>Украдите случайную карту у случайного соперника</t>
+  </si>
+  <si>
     <t>Нерф баланса: забираем корм</t>
   </si>
   <si>
@@ -256,6 +307,21 @@
     <t>Заберите 5 кормов у всех оппонентов</t>
   </si>
   <si>
+    <t>Инвестиции от Искандера</t>
+  </si>
+  <si>
+    <t>GET 30</t>
+  </si>
+  <si>
+    <t>Flux_iskander-as-angel-investor-with-golden-briefcase_-sparkles_-.png</t>
+  </si>
+  <si>
+    <t>Искандер верит в ваш проект! Крупные инвестиции.</t>
+  </si>
+  <si>
+    <t>Получите 30 корма из банка</t>
+  </si>
+  <si>
     <t>Дедлайн вчера: конфискация</t>
   </si>
   <si>
@@ -329,72 +395,6 @@
   </si>
   <si>
     <t>Заберите 10 кормов у всех оппонентов</t>
-  </si>
-  <si>
-    <t>Плагиат на митапе</t>
-  </si>
-  <si>
-    <t>Purple</t>
-  </si>
-  <si>
-    <t>STEAL_CARD RANDOM</t>
-  </si>
-  <si>
-    <t>Flux_mysterious-silhouette-sneaking-a-card-from-table_-purple-neo.png</t>
-  </si>
-  <si>
-    <t>Пока все обсуждали архитектуру, вы тихонько взяли чужую идею...</t>
-  </si>
-  <si>
-    <t>Украдите случайную карту у случайного соперника</t>
-  </si>
-  <si>
-    <t>Стипендия за проект</t>
-  </si>
-  <si>
-    <t>Gold</t>
-  </si>
-  <si>
-    <t>GET 6</t>
-  </si>
-  <si>
-    <t>Flux_golden-coin-with-game-controller-icon_-radiant-light_-cartoo.png</t>
-  </si>
-  <si>
-    <t>Ваш проект заметили! Первая выплата.</t>
-  </si>
-  <si>
-    <t>Получите 10 корма из банка</t>
-  </si>
-  <si>
-    <t>Грант на балансировку</t>
-  </si>
-  <si>
-    <t>GET 18</t>
-  </si>
-  <si>
-    <t>Flux_grant-document-with-golden-seal_-iskander-signing_-cartoon-s.png</t>
-  </si>
-  <si>
-    <t>Специальный грант на улучшение баланса.</t>
-  </si>
-  <si>
-    <t>Получите 20 корма из банка</t>
-  </si>
-  <si>
-    <t>Инвестиции от Искандера</t>
-  </si>
-  <si>
-    <t>GET 30</t>
-  </si>
-  <si>
-    <t>Flux_iskander-as-angel-investor-with-golden-briefcase_-sparkles_-.png</t>
-  </si>
-  <si>
-    <t>Искандер верит в ваш проект! Крупные инвестиции.</t>
-  </si>
-  <si>
-    <t>Получите 30 корма из банка</t>
   </si>
 </sst>
 </file>
@@ -662,9 +662,9 @@
       <rgbColor rgb="ffa5a5a5"/>
       <rgbColor rgb="ff3f3f3f"/>
       <rgbColor rgb="ff56c1fe"/>
+      <rgbColor rgb="fffff056"/>
       <rgbColor rgb="ffff968c"/>
       <rgbColor rgb="ffff94ca"/>
-      <rgbColor rgb="fffff056"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -1787,641 +1787,641 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" ht="76" customHeight="1">
-      <c r="A4" t="s" s="7">
+    <row r="4" ht="100" customHeight="1">
+      <c r="A4" t="s" s="11">
         <v>19</v>
       </c>
-      <c r="B4" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s" s="9">
+      <c r="B4" t="s" s="12">
         <v>20</v>
       </c>
-      <c r="D4" s="10">
-        <v>2</v>
-      </c>
-      <c r="E4" s="10">
-        <v>3</v>
-      </c>
-      <c r="F4" t="s" s="9">
+      <c r="C4" t="s" s="13">
         <v>21</v>
       </c>
-      <c r="G4" t="s" s="9">
+      <c r="D4" s="14">
+        <v>1</v>
+      </c>
+      <c r="E4" s="14">
+        <v>6</v>
+      </c>
+      <c r="F4" t="s" s="13">
         <v>22</v>
       </c>
-      <c r="H4" s="10">
-        <v>5</v>
-      </c>
-      <c r="I4" t="s" s="9">
+      <c r="G4" t="s" s="13">
         <v>23</v>
+      </c>
+      <c r="H4" s="14">
+        <v>50</v>
+      </c>
+      <c r="I4" t="s" s="13">
+        <v>24</v>
       </c>
     </row>
     <row r="5" ht="76" customHeight="1">
       <c r="A5" t="s" s="7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s" s="8">
         <v>10</v>
       </c>
       <c r="C5" t="s" s="9">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="10">
         <v>2</v>
       </c>
       <c r="E5" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" t="s" s="9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G5" t="s" s="9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H5" s="10">
         <v>5</v>
       </c>
       <c r="I5" t="s" s="9">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
-    <row r="6" ht="52" customHeight="1">
+    <row r="6" ht="76" customHeight="1">
       <c r="A6" t="s" s="7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s" s="8">
         <v>10</v>
       </c>
       <c r="C6" t="s" s="9">
+        <v>31</v>
+      </c>
+      <c r="D6" s="10">
+        <v>2</v>
+      </c>
+      <c r="E6" s="10">
+        <v>4</v>
+      </c>
+      <c r="F6" t="s" s="9">
+        <v>32</v>
+      </c>
+      <c r="G6" t="s" s="9">
+        <v>33</v>
+      </c>
+      <c r="H6" s="10">
+        <v>5</v>
+      </c>
+      <c r="I6" t="s" s="9">
         <v>29</v>
       </c>
-      <c r="D6" s="10">
-        <v>3</v>
-      </c>
-      <c r="E6" s="10">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s" s="9">
+    </row>
+    <row r="7" ht="88" customHeight="1">
+      <c r="A7" t="s" s="15">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s" s="16">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s" s="17">
+        <v>36</v>
+      </c>
+      <c r="D7" s="18">
+        <v>2</v>
+      </c>
+      <c r="E7" s="18">
+        <v>4</v>
+      </c>
+      <c r="F7" t="s" s="17">
+        <v>37</v>
+      </c>
+      <c r="G7" t="s" s="17">
+        <v>38</v>
+      </c>
+      <c r="H7" s="18">
         <v>30</v>
       </c>
-      <c r="G6" t="s" s="9">
-        <v>31</v>
-      </c>
-      <c r="H6" s="10">
-        <v>10</v>
-      </c>
-      <c r="I6" t="s" s="9">
-        <v>32</v>
+      <c r="I7" t="s" s="17">
+        <v>39</v>
       </c>
     </row>
-    <row r="7" ht="76" customHeight="1">
-      <c r="A7" t="s" s="7">
-        <v>33</v>
-      </c>
-      <c r="B7" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="C7" t="s" s="9">
-        <v>34</v>
-      </c>
-      <c r="D7" s="10">
-        <v>3</v>
-      </c>
-      <c r="E7" s="10">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s" s="9">
-        <v>35</v>
-      </c>
-      <c r="G7" t="s" s="9">
-        <v>36</v>
-      </c>
-      <c r="H7" s="10">
-        <v>10</v>
-      </c>
-      <c r="I7" t="s" s="9">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" ht="88" customHeight="1">
+    <row r="8" ht="52" customHeight="1">
       <c r="A8" t="s" s="7">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s" s="8">
         <v>10</v>
       </c>
       <c r="C8" t="s" s="9">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D8" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8" s="10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s" s="9">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G8" t="s" s="9">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H8" s="10">
         <v>10</v>
       </c>
       <c r="I8" t="s" s="9">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" ht="76" customHeight="1">
       <c r="A9" t="s" s="7">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s" s="8">
         <v>10</v>
       </c>
       <c r="C9" t="s" s="9">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D9" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9" s="10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s" s="9">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G9" t="s" s="9">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H9" s="10">
         <v>10</v>
       </c>
       <c r="I9" t="s" s="9">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="10" ht="76" customHeight="1">
-      <c r="A10" t="s" s="7">
-        <v>46</v>
-      </c>
-      <c r="B10" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="C10" t="s" s="9">
-        <v>47</v>
-      </c>
-      <c r="D10" s="10">
-        <v>5</v>
-      </c>
-      <c r="E10" s="10">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s" s="9">
-        <v>48</v>
-      </c>
-      <c r="G10" t="s" s="9">
+    <row r="10" ht="88" customHeight="1">
+      <c r="A10" t="s" s="15">
         <v>49</v>
       </c>
-      <c r="H10" s="10">
-        <v>10</v>
-      </c>
-      <c r="I10" t="s" s="9">
+      <c r="B10" t="s" s="16">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s" s="17">
         <v>50</v>
       </c>
+      <c r="D10" s="18">
+        <v>3</v>
+      </c>
+      <c r="E10" s="18">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s" s="17">
+        <v>51</v>
+      </c>
+      <c r="G10" t="s" s="17">
+        <v>52</v>
+      </c>
+      <c r="H10" s="18">
+        <v>30</v>
+      </c>
+      <c r="I10" t="s" s="17">
+        <v>53</v>
+      </c>
     </row>
-    <row r="11" ht="64" customHeight="1">
+    <row r="11" ht="88" customHeight="1">
       <c r="A11" t="s" s="7">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s" s="8">
         <v>10</v>
       </c>
       <c r="C11" t="s" s="9">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D11" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" s="10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s" s="9">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G11" t="s" s="9">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H11" s="10">
         <v>10</v>
       </c>
       <c r="I11" t="s" s="9">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
-    <row r="12" ht="88" customHeight="1">
-      <c r="A12" t="s" s="11">
-        <v>55</v>
-      </c>
-      <c r="B12" t="s" s="12">
-        <v>56</v>
-      </c>
-      <c r="C12" t="s" s="13">
-        <v>57</v>
-      </c>
-      <c r="D12" s="14">
-        <v>2</v>
-      </c>
-      <c r="E12" s="14">
+    <row r="12" ht="76" customHeight="1">
+      <c r="A12" t="s" s="7">
+        <v>59</v>
+      </c>
+      <c r="B12" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s" s="9">
+        <v>60</v>
+      </c>
+      <c r="D12" s="10">
         <v>4</v>
       </c>
-      <c r="F12" t="s" s="13">
+      <c r="E12" s="10">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s" s="9">
+        <v>61</v>
+      </c>
+      <c r="G12" t="s" s="9">
+        <v>62</v>
+      </c>
+      <c r="H12" s="10">
+        <v>10</v>
+      </c>
+      <c r="I12" t="s" s="9">
         <v>58</v>
       </c>
-      <c r="G12" t="s" s="13">
-        <v>59</v>
-      </c>
-      <c r="H12" s="14">
-        <v>30</v>
-      </c>
-      <c r="I12" t="s" s="13">
-        <v>60</v>
-      </c>
     </row>
-    <row r="13" ht="88" customHeight="1">
-      <c r="A13" t="s" s="11">
-        <v>61</v>
-      </c>
-      <c r="B13" t="s" s="12">
-        <v>56</v>
-      </c>
-      <c r="C13" t="s" s="13">
-        <v>62</v>
-      </c>
-      <c r="D13" s="14">
-        <v>3</v>
-      </c>
-      <c r="E13" s="14">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s" s="13">
+    <row r="13" ht="76" customHeight="1">
+      <c r="A13" t="s" s="7">
         <v>63</v>
       </c>
-      <c r="G13" t="s" s="13">
+      <c r="B13" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s" s="9">
         <v>64</v>
       </c>
-      <c r="H13" s="14">
-        <v>30</v>
-      </c>
-      <c r="I13" t="s" s="13">
+      <c r="D13" s="10">
+        <v>5</v>
+      </c>
+      <c r="E13" s="10">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s" s="9">
         <v>65</v>
       </c>
+      <c r="G13" t="s" s="9">
+        <v>66</v>
+      </c>
+      <c r="H13" s="10">
+        <v>10</v>
+      </c>
+      <c r="I13" t="s" s="9">
+        <v>67</v>
+      </c>
     </row>
-    <row r="14" ht="88" customHeight="1">
-      <c r="A14" t="s" s="11">
-        <v>66</v>
-      </c>
-      <c r="B14" t="s" s="12">
-        <v>56</v>
-      </c>
-      <c r="C14" t="s" s="13">
+    <row r="14" ht="64" customHeight="1">
+      <c r="A14" t="s" s="7">
+        <v>68</v>
+      </c>
+      <c r="B14" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="C14" t="s" s="9">
+        <v>69</v>
+      </c>
+      <c r="D14" s="10">
+        <v>5</v>
+      </c>
+      <c r="E14" s="10">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s" s="9">
+        <v>70</v>
+      </c>
+      <c r="G14" t="s" s="9">
+        <v>71</v>
+      </c>
+      <c r="H14" s="10">
+        <v>10</v>
+      </c>
+      <c r="I14" t="s" s="9">
         <v>67</v>
-      </c>
-      <c r="D14" s="14">
-        <v>6</v>
-      </c>
-      <c r="E14" s="14">
-        <v>12</v>
-      </c>
-      <c r="F14" t="s" s="13">
-        <v>68</v>
-      </c>
-      <c r="G14" t="s" s="13">
-        <v>69</v>
-      </c>
-      <c r="H14" s="14">
-        <v>30</v>
-      </c>
-      <c r="I14" t="s" s="13">
-        <v>70</v>
       </c>
     </row>
     <row r="15" ht="100" customHeight="1">
       <c r="A15" t="s" s="11">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B15" t="s" s="12">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s" s="13">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E15" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F15" t="s" s="13">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G15" t="s" s="13">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H15" s="14">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I15" t="s" s="13">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" ht="88" customHeight="1">
-      <c r="A16" t="s" s="11">
-        <v>76</v>
-      </c>
-      <c r="B16" t="s" s="12">
-        <v>56</v>
-      </c>
-      <c r="C16" t="s" s="13">
+      <c r="A16" t="s" s="15">
         <v>77</v>
       </c>
-      <c r="D16" s="14">
-        <v>10</v>
-      </c>
-      <c r="E16" s="14">
-        <v>20</v>
-      </c>
-      <c r="F16" t="s" s="13">
+      <c r="B16" t="s" s="16">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s" s="17">
         <v>78</v>
       </c>
-      <c r="G16" t="s" s="13">
+      <c r="D16" s="18">
+        <v>6</v>
+      </c>
+      <c r="E16" s="18">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s" s="17">
         <v>79</v>
       </c>
-      <c r="H16" s="14">
+      <c r="G16" t="s" s="17">
+        <v>80</v>
+      </c>
+      <c r="H16" s="18">
         <v>30</v>
       </c>
-      <c r="I16" t="s" s="13">
-        <v>80</v>
+      <c r="I16" t="s" s="17">
+        <v>81</v>
       </c>
     </row>
     <row r="17" ht="100" customHeight="1">
-      <c r="A17" t="s" s="11">
-        <v>81</v>
-      </c>
-      <c r="B17" t="s" s="12">
-        <v>56</v>
-      </c>
-      <c r="C17" t="s" s="13">
+      <c r="A17" t="s" s="15">
         <v>82</v>
       </c>
-      <c r="D17" s="14">
+      <c r="B17" t="s" s="16">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s" s="17">
+        <v>83</v>
+      </c>
+      <c r="D17" s="18">
+        <v>8</v>
+      </c>
+      <c r="E17" s="18">
+        <v>16</v>
+      </c>
+      <c r="F17" t="s" s="17">
+        <v>84</v>
+      </c>
+      <c r="G17" t="s" s="17">
+        <v>85</v>
+      </c>
+      <c r="H17" s="18">
+        <v>30</v>
+      </c>
+      <c r="I17" t="s" s="17">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" ht="88" customHeight="1">
+      <c r="A18" t="s" s="19">
+        <v>87</v>
+      </c>
+      <c r="B18" t="s" s="20">
+        <v>88</v>
+      </c>
+      <c r="C18" t="s" s="21">
+        <v>89</v>
+      </c>
+      <c r="D18" s="22">
+        <v>3</v>
+      </c>
+      <c r="E18" s="22">
+        <v>200</v>
+      </c>
+      <c r="F18" t="s" s="21">
+        <v>90</v>
+      </c>
+      <c r="G18" t="s" s="21">
+        <v>91</v>
+      </c>
+      <c r="H18" s="22">
+        <v>300</v>
+      </c>
+      <c r="I18" t="s" s="21">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" ht="88" customHeight="1">
+      <c r="A19" t="s" s="15">
+        <v>93</v>
+      </c>
+      <c r="B19" t="s" s="16">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s" s="17">
+        <v>94</v>
+      </c>
+      <c r="D19" s="18">
+        <v>10</v>
+      </c>
+      <c r="E19" s="18">
+        <v>20</v>
+      </c>
+      <c r="F19" t="s" s="17">
+        <v>95</v>
+      </c>
+      <c r="G19" t="s" s="17">
+        <v>96</v>
+      </c>
+      <c r="H19" s="18">
+        <v>30</v>
+      </c>
+      <c r="I19" t="s" s="17">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" ht="88" customHeight="1">
+      <c r="A20" t="s" s="11">
+        <v>98</v>
+      </c>
+      <c r="B20" t="s" s="12">
+        <v>20</v>
+      </c>
+      <c r="C20" t="s" s="13">
+        <v>99</v>
+      </c>
+      <c r="D20" s="14">
+        <v>10</v>
+      </c>
+      <c r="E20" s="14">
+        <v>30</v>
+      </c>
+      <c r="F20" t="s" s="13">
+        <v>100</v>
+      </c>
+      <c r="G20" t="s" s="13">
+        <v>101</v>
+      </c>
+      <c r="H20" s="14">
+        <v>50</v>
+      </c>
+      <c r="I20" t="s" s="13">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" ht="100" customHeight="1">
+      <c r="A21" t="s" s="15">
+        <v>103</v>
+      </c>
+      <c r="B21" t="s" s="16">
+        <v>35</v>
+      </c>
+      <c r="C21" t="s" s="17">
+        <v>104</v>
+      </c>
+      <c r="D21" s="18">
         <v>12</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E21" s="18">
         <v>24</v>
       </c>
-      <c r="F17" t="s" s="13">
-        <v>83</v>
-      </c>
-      <c r="G17" t="s" s="13">
-        <v>84</v>
-      </c>
-      <c r="H17" s="14">
+      <c r="F21" t="s" s="17">
+        <v>105</v>
+      </c>
+      <c r="G21" t="s" s="17">
+        <v>106</v>
+      </c>
+      <c r="H21" s="18">
         <v>30</v>
       </c>
-      <c r="I17" t="s" s="13">
-        <v>85</v>
+      <c r="I21" t="s" s="17">
+        <v>107</v>
       </c>
     </row>
-    <row r="18" ht="100" customHeight="1">
-      <c r="A18" t="s" s="11">
-        <v>86</v>
-      </c>
-      <c r="B18" t="s" s="12">
-        <v>56</v>
-      </c>
-      <c r="C18" t="s" s="13">
-        <v>87</v>
-      </c>
-      <c r="D18" s="14">
+    <row r="22" ht="100" customHeight="1">
+      <c r="A22" t="s" s="15">
+        <v>108</v>
+      </c>
+      <c r="B22" t="s" s="16">
+        <v>35</v>
+      </c>
+      <c r="C22" t="s" s="17">
+        <v>109</v>
+      </c>
+      <c r="D22" s="18">
         <v>14</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E22" s="18">
         <v>28</v>
       </c>
-      <c r="F18" t="s" s="13">
-        <v>88</v>
-      </c>
-      <c r="G18" t="s" s="13">
-        <v>89</v>
-      </c>
-      <c r="H18" s="14">
+      <c r="F22" t="s" s="17">
+        <v>110</v>
+      </c>
+      <c r="G22" t="s" s="17">
+        <v>111</v>
+      </c>
+      <c r="H22" s="18">
         <v>30</v>
       </c>
-      <c r="I18" t="s" s="13">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="19" ht="100" customHeight="1">
-      <c r="A19" t="s" s="11">
-        <v>91</v>
-      </c>
-      <c r="B19" t="s" s="12">
-        <v>56</v>
-      </c>
-      <c r="C19" t="s" s="13">
-        <v>92</v>
-      </c>
-      <c r="D19" s="14">
-        <v>16</v>
-      </c>
-      <c r="E19" s="14">
-        <v>32</v>
-      </c>
-      <c r="F19" t="s" s="13">
-        <v>93</v>
-      </c>
-      <c r="G19" t="s" s="13">
-        <v>94</v>
-      </c>
-      <c r="H19" s="14">
-        <v>30</v>
-      </c>
-      <c r="I19" t="s" s="13">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="20" ht="100" customHeight="1">
-      <c r="A20" t="s" s="11">
-        <v>96</v>
-      </c>
-      <c r="B20" t="s" s="12">
-        <v>56</v>
-      </c>
-      <c r="C20" t="s" s="13">
-        <v>97</v>
-      </c>
-      <c r="D20" s="14">
-        <v>18</v>
-      </c>
-      <c r="E20" s="14">
-        <v>36</v>
-      </c>
-      <c r="F20" t="s" s="13">
-        <v>98</v>
-      </c>
-      <c r="G20" t="s" s="13">
-        <v>99</v>
-      </c>
-      <c r="H20" s="14">
-        <v>30</v>
-      </c>
-      <c r="I20" t="s" s="13">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" ht="88" customHeight="1">
-      <c r="A21" t="s" s="11">
-        <v>101</v>
-      </c>
-      <c r="B21" t="s" s="12">
-        <v>56</v>
-      </c>
-      <c r="C21" t="s" s="13">
-        <v>102</v>
-      </c>
-      <c r="D21" s="14">
-        <v>20</v>
-      </c>
-      <c r="E21" s="14">
-        <v>40</v>
-      </c>
-      <c r="F21" t="s" s="13">
-        <v>103</v>
-      </c>
-      <c r="G21" t="s" s="13">
-        <v>104</v>
-      </c>
-      <c r="H21" s="14">
-        <v>30</v>
-      </c>
-      <c r="I21" t="s" s="13">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="22" ht="88" customHeight="1">
-      <c r="A22" t="s" s="15">
-        <v>106</v>
-      </c>
-      <c r="B22" t="s" s="16">
-        <v>107</v>
-      </c>
-      <c r="C22" t="s" s="17">
-        <v>108</v>
-      </c>
-      <c r="D22" s="18">
-        <v>8</v>
-      </c>
-      <c r="E22" s="18">
-        <v>200</v>
-      </c>
-      <c r="F22" t="s" s="17">
-        <v>109</v>
-      </c>
-      <c r="G22" t="s" s="17">
-        <v>110</v>
-      </c>
-      <c r="H22" s="18">
-        <v>15</v>
-      </c>
       <c r="I22" t="s" s="17">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" ht="100" customHeight="1">
-      <c r="A23" t="s" s="19">
-        <v>112</v>
-      </c>
-      <c r="B23" t="s" s="20">
+      <c r="A23" t="s" s="15">
         <v>113</v>
       </c>
-      <c r="C23" t="s" s="21">
+      <c r="B23" t="s" s="16">
+        <v>35</v>
+      </c>
+      <c r="C23" t="s" s="17">
         <v>114</v>
       </c>
-      <c r="D23" s="22">
-        <v>1</v>
-      </c>
-      <c r="E23" s="22">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s" s="21">
+      <c r="D23" s="18">
+        <v>16</v>
+      </c>
+      <c r="E23" s="18">
+        <v>32</v>
+      </c>
+      <c r="F23" t="s" s="17">
         <v>115</v>
       </c>
-      <c r="G23" t="s" s="21">
+      <c r="G23" t="s" s="17">
         <v>116</v>
       </c>
-      <c r="H23" s="22">
-        <v>50</v>
-      </c>
-      <c r="I23" t="s" s="21">
+      <c r="H23" s="18">
+        <v>30</v>
+      </c>
+      <c r="I23" t="s" s="17">
         <v>117</v>
       </c>
     </row>
     <row r="24" ht="100" customHeight="1">
-      <c r="A24" t="s" s="19">
+      <c r="A24" t="s" s="15">
         <v>118</v>
       </c>
-      <c r="B24" t="s" s="20">
-        <v>113</v>
-      </c>
-      <c r="C24" t="s" s="21">
+      <c r="B24" t="s" s="16">
+        <v>35</v>
+      </c>
+      <c r="C24" t="s" s="17">
         <v>119</v>
       </c>
-      <c r="D24" s="22">
-        <v>5</v>
-      </c>
-      <c r="E24" s="22">
+      <c r="D24" s="18">
         <v>18</v>
       </c>
-      <c r="F24" t="s" s="21">
+      <c r="E24" s="18">
+        <v>36</v>
+      </c>
+      <c r="F24" t="s" s="17">
         <v>120</v>
       </c>
-      <c r="G24" t="s" s="21">
+      <c r="G24" t="s" s="17">
         <v>121</v>
       </c>
-      <c r="H24" s="22">
-        <v>50</v>
-      </c>
-      <c r="I24" t="s" s="21">
+      <c r="H24" s="18">
+        <v>30</v>
+      </c>
+      <c r="I24" t="s" s="17">
         <v>122</v>
       </c>
     </row>
     <row r="25" ht="88" customHeight="1">
-      <c r="A25" t="s" s="19">
+      <c r="A25" t="s" s="15">
         <v>123</v>
       </c>
-      <c r="B25" t="s" s="20">
-        <v>113</v>
-      </c>
-      <c r="C25" t="s" s="21">
+      <c r="B25" t="s" s="16">
+        <v>35</v>
+      </c>
+      <c r="C25" t="s" s="17">
         <v>124</v>
       </c>
-      <c r="D25" s="22">
-        <v>10</v>
-      </c>
-      <c r="E25" s="22">
+      <c r="D25" s="18">
+        <v>20</v>
+      </c>
+      <c r="E25" s="18">
+        <v>40</v>
+      </c>
+      <c r="F25" t="s" s="17">
+        <v>125</v>
+      </c>
+      <c r="G25" t="s" s="17">
+        <v>126</v>
+      </c>
+      <c r="H25" s="18">
         <v>30</v>
       </c>
-      <c r="F25" t="s" s="21">
-        <v>125</v>
-      </c>
-      <c r="G25" t="s" s="21">
-        <v>126</v>
-      </c>
-      <c r="H25" s="22">
-        <v>50</v>
-      </c>
-      <c r="I25" t="s" s="21">
+      <c r="I25" t="s" s="17">
         <v>127</v>
       </c>
     </row>
